--- a/Template_Migrasi_Final_Revisi.xlsx
+++ b/Template_Migrasi_Final_Revisi.xlsx
@@ -22,8 +22,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Nasabah'!$A$2:$G$1000</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pinjaman'!$A$2:$N$1000</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Angsuran_Historis'!$A$2:$K$1000</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pinjaman'!$A$2:$O$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Angsuran_Historis'!$A$2:$K$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Saldo_Awal_Kas'!$A$2:$F$1000</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Konfigurasi_Koperasi'!$A$2:$F$1000</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Master_Produk'!$A$2:$J$1000</definedName>
@@ -39,10 +39,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="\R\p\ #,##0;[Red]\-\R\p\ #,##0"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="Rp #,##0;[Red]-Rp #,##0"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -158,8 +161,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -217,6 +223,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -353,7 +369,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -447,6 +463,25 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="11" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1049,7 +1084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" style="32" min="1" max="1"/>
@@ -1183,13 +1218,17 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="35.15" customHeight="1" s="32">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="13" ht="48" customHeight="1" s="32">
+      <c r="A13" s="40" t="inlineStr">
         <is>
           <t>Nominal</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n"/>
+      <c r="B13" s="41" t="inlineStr">
+        <is>
+          <t>Isi nominal rupiah penuh. Contoh: 112500 (bukan 112.5). Denda contoh: 1500.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="35.15" customHeight="1" s="32">
       <c r="A14" s="8" t="inlineStr">
@@ -1224,6 +1263,78 @@
       <c r="B16" t="inlineStr">
         <is>
           <t>Isi path relatif uploads (contoh: anggota/ktp-xxx.jpg). Untuk pindah hosting gunakan Backup ZIP lengkap agar file ikut.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1" s="32">
+      <c r="A17" s="40" t="inlineStr">
+        <is>
+          <t>Foto &amp; dokumen</t>
+        </is>
+      </c>
+      <c r="B17" s="41" t="inlineStr">
+        <is>
+          <t>Path foto di kolom Nasabah/Pinjaman harus relatif ke folder uploads/ (contoh: anggota/25/ktp.jpg). Setelah Reset Total: JANGAN hapus folder uploads/. Biarkan kolom Foto kosong jika ingin dipulihkan otomatis dari cadangan (kode anggota/pinjaman sama). Jika foto tidak tampil di modal, file fisik hilang — restore uploads atau unggah ulang di Data Anggota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1" s="32">
+      <c r="A18" s="40" t="inlineStr">
+        <is>
+          <t>Laporan denda</t>
+        </is>
+      </c>
+      <c r="B18" s="41" t="inlineStr">
+        <is>
+          <t>Isi kolom Denda (Rp) pada Angsuran_Historis bila nasabah kena denda. Contoh wajib: SOLIKAH 1.500 tgl 25/09/2026 dan MASLUKAH 1.500 tgl 15/10/2026. Import akan mencatat ke layanan_bayar_denda agar muncul di Laporan Denda. Cetak/PDF ada di kolom Aksi per baris (bukan tombol global).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1" s="32">
+      <c r="A19" s="40" t="inlineStr">
+        <is>
+          <t>Status lunas vs pelunasan</t>
+        </is>
+      </c>
+      <c r="B19" s="41" t="inlineStr">
+        <is>
+          <t>Jenis Pembayaran = cicilan → di laporan/detail berstatus Lunas normal. Jenis Pembayaran = pelunasan → status Pelunasan (sisa tenor dilunasi sekaligus). Contoh Sobiroh: angsuran 1–4 cicilan, ke-5 pelunasan. Jangan menandai semua baris sebagai pelunasan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1" s="32">
+      <c r="A20" s="40" t="inlineStr">
+        <is>
+          <t>Data yang dibersihkan</t>
+        </is>
+      </c>
+      <c r="B20" s="41" t="inlineStr">
+        <is>
+          <t>Dihapus dari template agar sesuai real: 2 pinjaman lunas Warsingah (PJN-20261024-0021 &amp; PJN-20261026-0023) dan Retno lunas tgl 18/10 (PJN-20261018-0015). Warsingah aktif (PJN-20261028-0025) dan Retno lunas 23/10 (0016) tetap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1" s="32">
+      <c r="A21" s="40" t="inlineStr">
+        <is>
+          <t>Historis 29/10/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="41" t="inlineStr">
+        <is>
+          <t>Sudah ditambahkan: Elis cicilan 112.500, Noviani cicilan 225.000, UMAINAH pelunasan sisa tenor (pinjaman ditandai lunas). Import ulang file ini besok siang setelah Reset Total + cadangan dokumen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1" s="32">
+      <c r="A22" s="40" t="inlineStr">
+        <is>
+          <t>Surat &amp; notifikasi</t>
+        </is>
+      </c>
+      <c r="B22" s="41" t="inlineStr">
+        <is>
+          <t>Setelah import, sistem mengisi template Surat Keterangan Lunas bila kosong. Notifikasi Admin/Teller/Anggota mengikuti data hasil import (pengajuan, denda, jatuh tempo, dll).</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" style="32" min="1" max="1"/>
@@ -1693,6 +1804,66 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>Path foto KTP/KK/pasangan &amp; pencairan dari SQL; file fisik tetap di folder uploads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DIHAPUS_LUNAS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Warsingah PJN-20261024-0021 &amp; PJN-20261026-0023; Retno PJN-20261018-0015 (tgl 18/10) — agar laporan lunas tidak numpuk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DENDA_HISTORIS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SOLIKAH denda 1500 tgl 25/09/2026; MASLUKAH denda 1500 tgl 15/10/2026 (Angsuran_Historis → laporan denda).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HISTORIS_29OKT</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Elis 112500 cicilan; Noviani 225000 cicilan; UMAINAH pelunasan + status pinjaman lunas 29/10/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STATUS_BAYAR</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>cicilan = Lunas normal; pelunasan = Pelunasan (contoh Sobiroh 1-4 cicilan, 5 pelunasan).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FOTO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Jangan hapus uploads/ saat reset. Path di Excel opsional jika cadangan kode anggota sama.</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col width="20" customWidth="1" style="32" min="1" max="2"/>
@@ -2771,1384 +2942,1201 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1" s="32">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="42" t="inlineStr">
         <is>
           <t>PJN-20261013-0001</t>
         </is>
       </c>
-      <c r="B3" s="39" t="inlineStr">
+      <c r="B3" s="42" t="inlineStr">
         <is>
           <t>AGT0001</t>
         </is>
       </c>
-      <c r="C3" s="39" t="inlineStr">
+      <c r="C3" s="42" t="inlineStr">
         <is>
           <t>SPHP 222</t>
         </is>
       </c>
-      <c r="D3" s="39" t="inlineStr">
+      <c r="D3" s="43" t="inlineStr">
         <is>
           <t>10/09/2026</t>
         </is>
       </c>
-      <c r="E3" s="39" t="n">
+      <c r="E3" s="44" t="n">
         <v>2000000</v>
       </c>
-      <c r="F3" s="39" t="n">
+      <c r="F3" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="G3" s="39" t="inlineStr">
+      <c r="G3" s="42" t="inlineStr">
         <is>
           <t>mingguan</t>
         </is>
       </c>
-      <c r="H3" s="39" t="n">
+      <c r="H3" s="42" t="n">
         <v>35</v>
       </c>
-      <c r="I3" s="39" t="inlineStr">
+      <c r="I3" s="42" t="inlineStr">
         <is>
           <t>flat</t>
         </is>
       </c>
-      <c r="J3" s="39" t="n">
+      <c r="J3" s="44" t="n">
         <v>225000</v>
       </c>
-      <c r="K3" s="39" t="n">
+      <c r="K3" s="44" t="n">
         <v>2700000</v>
       </c>
-      <c r="L3" s="39" t="inlineStr">
+      <c r="L3" s="42" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="M3" s="45" t="n">
+        <v>46324</v>
+      </c>
+      <c r="N3" s="41" t="inlineStr">
+        <is>
+          <t>pencairan/153a3c38261a6c164e04faec7b7deea7.png</t>
+        </is>
+      </c>
+      <c r="O3" s="41" t="inlineStr">
+        <is>
+          <t>Lunas 29/10/2026 (pelunasan sisa tenor).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0009</t>
+        </is>
+      </c>
+      <c r="B4" s="42" t="inlineStr">
+        <is>
+          <t>AGT0007</t>
+        </is>
+      </c>
+      <c r="C4" s="42" t="inlineStr">
+        <is>
+          <t>SPHP 222</t>
+        </is>
+      </c>
+      <c r="D4" s="43" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="E4" s="44" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="F4" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" s="42" t="inlineStr">
+        <is>
+          <t>mingguan</t>
+        </is>
+      </c>
+      <c r="H4" s="42" t="n">
+        <v>35</v>
+      </c>
+      <c r="I4" s="42" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="J4" s="44" t="n">
+        <v>225000</v>
+      </c>
+      <c r="K4" s="44" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="L4" s="42" t="inlineStr">
         <is>
           <t>aktif</t>
         </is>
       </c>
-      <c r="M3" s="39" t="inlineStr"/>
-      <c r="N3" s="39" t="inlineStr">
-        <is>
-          <t>pencairan/153a3c38261a6c164e04faec7b7deea7.png</t>
-        </is>
-      </c>
-      <c r="O3" s="39" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0009</t>
-        </is>
-      </c>
-      <c r="B4" s="39" t="inlineStr">
-        <is>
-          <t>AGT0007</t>
-        </is>
-      </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="M4" s="41" t="n"/>
+      <c r="N4" s="41" t="inlineStr">
+        <is>
+          <t>pencairan/54e9eecdb4bba08284c9bf990df993e6.jpg</t>
+        </is>
+      </c>
+      <c r="O4" s="41" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0011</t>
+        </is>
+      </c>
+      <c r="B5" s="42" t="inlineStr">
+        <is>
+          <t>AGT0018</t>
+        </is>
+      </c>
+      <c r="C5" s="42" t="inlineStr">
+        <is>
+          <t>SPHP 111</t>
+        </is>
+      </c>
+      <c r="D5" s="43" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="E5" s="44" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F5" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="42" t="inlineStr">
+        <is>
+          <t>mingguan</t>
+        </is>
+      </c>
+      <c r="H5" s="42" t="n">
+        <v>35</v>
+      </c>
+      <c r="I5" s="42" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="J5" s="44" t="n">
+        <v>112500</v>
+      </c>
+      <c r="K5" s="44" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="L5" s="42" t="inlineStr">
+        <is>
+          <t>aktif</t>
+        </is>
+      </c>
+      <c r="M5" s="41" t="n"/>
+      <c r="N5" s="41" t="inlineStr">
+        <is>
+          <t>pencairan/2457c4049c3e0a6ff905afd679799931.png</t>
+        </is>
+      </c>
+      <c r="O5" s="41" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0010</t>
+        </is>
+      </c>
+      <c r="B6" s="42" t="inlineStr">
+        <is>
+          <t>AGT0006</t>
+        </is>
+      </c>
+      <c r="C6" s="42" t="inlineStr">
+        <is>
+          <t>SPHP 11</t>
+        </is>
+      </c>
+      <c r="D6" s="43" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="E6" s="44" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F6" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="42" t="inlineStr">
+        <is>
+          <t>mingguan</t>
+        </is>
+      </c>
+      <c r="H6" s="42" t="n">
+        <v>25</v>
+      </c>
+      <c r="I6" s="42" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="J6" s="44" t="n">
+        <v>156250</v>
+      </c>
+      <c r="K6" s="44" t="n">
+        <v>1250000</v>
+      </c>
+      <c r="L6" s="42" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="M6" s="45" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="N6" s="41" t="inlineStr">
+        <is>
+          <t>pencairan/d13534b7c79d70faa40a9b08d8d5f39d.png</t>
+        </is>
+      </c>
+      <c r="O6" s="41" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0014</t>
+        </is>
+      </c>
+      <c r="B7" s="42" t="inlineStr">
+        <is>
+          <t>AGT0015</t>
+        </is>
+      </c>
+      <c r="C7" s="42" t="inlineStr">
+        <is>
+          <t>SPHP 111</t>
+        </is>
+      </c>
+      <c r="D7" s="43" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="E7" s="44" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F7" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="42" t="inlineStr">
+        <is>
+          <t>mingguan</t>
+        </is>
+      </c>
+      <c r="H7" s="42" t="n">
+        <v>35</v>
+      </c>
+      <c r="I7" s="42" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="J7" s="44" t="n">
+        <v>112500</v>
+      </c>
+      <c r="K7" s="44" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="L7" s="42" t="inlineStr">
+        <is>
+          <t>aktif</t>
+        </is>
+      </c>
+      <c r="M7" s="41" t="n"/>
+      <c r="N7" s="41" t="inlineStr">
+        <is>
+          <t>pencairan/7e74657180eca4b8475a4044660b9a85.png</t>
+        </is>
+      </c>
+      <c r="O7" s="41" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0013</t>
+        </is>
+      </c>
+      <c r="B8" s="42" t="inlineStr">
+        <is>
+          <t>AGT0016</t>
+        </is>
+      </c>
+      <c r="C8" s="42" t="inlineStr">
+        <is>
+          <t>SPHP 111</t>
+        </is>
+      </c>
+      <c r="D8" s="43" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="E8" s="44" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F8" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="42" t="inlineStr">
+        <is>
+          <t>mingguan</t>
+        </is>
+      </c>
+      <c r="H8" s="42" t="n">
+        <v>35</v>
+      </c>
+      <c r="I8" s="42" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="J8" s="44" t="n">
+        <v>112500</v>
+      </c>
+      <c r="K8" s="44" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="L8" s="42" t="inlineStr">
+        <is>
+          <t>aktif</t>
+        </is>
+      </c>
+      <c r="M8" s="41" t="n"/>
+      <c r="N8" s="41" t="inlineStr">
+        <is>
+          <t>pencairan/974ee4497315fc9a44fd1b207dd4605a.png</t>
+        </is>
+      </c>
+      <c r="O8" s="41" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0012</t>
+        </is>
+      </c>
+      <c r="B9" s="42" t="inlineStr">
+        <is>
+          <t>AGT0017</t>
+        </is>
+      </c>
+      <c r="C9" s="42" t="inlineStr">
+        <is>
+          <t>SPHP 111</t>
+        </is>
+      </c>
+      <c r="D9" s="43" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="E9" s="44" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F9" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="42" t="inlineStr">
+        <is>
+          <t>mingguan</t>
+        </is>
+      </c>
+      <c r="H9" s="42" t="n">
+        <v>35</v>
+      </c>
+      <c r="I9" s="42" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="J9" s="44" t="n">
+        <v>112500</v>
+      </c>
+      <c r="K9" s="44" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="L9" s="42" t="inlineStr">
+        <is>
+          <t>aktif</t>
+        </is>
+      </c>
+      <c r="M9" s="41" t="n"/>
+      <c r="N9" s="41" t="inlineStr">
+        <is>
+          <t>pencairan/deb64ae0b0ff2718b1786b9142a2f5c7.png</t>
+        </is>
+      </c>
+      <c r="O9" s="41" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0008</t>
+        </is>
+      </c>
+      <c r="B10" s="42" t="inlineStr">
+        <is>
+          <t>AGT0008</t>
+        </is>
+      </c>
+      <c r="C10" s="42" t="inlineStr">
+        <is>
+          <t>SPHP 111</t>
+        </is>
+      </c>
+      <c r="D10" s="43" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="E10" s="44" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F10" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="42" t="inlineStr">
+        <is>
+          <t>mingguan</t>
+        </is>
+      </c>
+      <c r="H10" s="42" t="n">
+        <v>35</v>
+      </c>
+      <c r="I10" s="42" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="J10" s="44" t="n">
+        <v>112500</v>
+      </c>
+      <c r="K10" s="44" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="L10" s="42" t="inlineStr">
+        <is>
+          <t>aktif</t>
+        </is>
+      </c>
+      <c r="M10" s="41" t="n"/>
+      <c r="N10" s="41" t="inlineStr">
+        <is>
+          <t>pencairan/17864ddf79fc06d7c95b368255bcca73.png</t>
+        </is>
+      </c>
+      <c r="O10" s="41" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0007</t>
+        </is>
+      </c>
+      <c r="B11" s="42" t="inlineStr">
+        <is>
+          <t>AGT0009</t>
+        </is>
+      </c>
+      <c r="C11" s="42" t="inlineStr">
+        <is>
+          <t>SPHP 111</t>
+        </is>
+      </c>
+      <c r="D11" s="43" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="E11" s="44" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F11" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="42" t="inlineStr">
+        <is>
+          <t>mingguan</t>
+        </is>
+      </c>
+      <c r="H11" s="42" t="n">
+        <v>35</v>
+      </c>
+      <c r="I11" s="42" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="J11" s="44" t="n">
+        <v>112500</v>
+      </c>
+      <c r="K11" s="44" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="L11" s="42" t="inlineStr">
+        <is>
+          <t>aktif</t>
+        </is>
+      </c>
+      <c r="M11" s="41" t="n"/>
+      <c r="N11" s="41" t="inlineStr">
+        <is>
+          <t>pencairan/c8976ddcde2e1ab8d107de82965cac32.png</t>
+        </is>
+      </c>
+      <c r="O11" s="41" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0006</t>
+        </is>
+      </c>
+      <c r="B12" s="42" t="inlineStr">
+        <is>
+          <t>AGT0010</t>
+        </is>
+      </c>
+      <c r="C12" s="42" t="inlineStr">
+        <is>
+          <t>SPHP 111</t>
+        </is>
+      </c>
+      <c r="D12" s="43" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="E12" s="44" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F12" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="42" t="inlineStr">
+        <is>
+          <t>mingguan</t>
+        </is>
+      </c>
+      <c r="H12" s="42" t="n">
+        <v>35</v>
+      </c>
+      <c r="I12" s="42" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="J12" s="44" t="n">
+        <v>112500</v>
+      </c>
+      <c r="K12" s="44" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="L12" s="42" t="inlineStr">
+        <is>
+          <t>aktif</t>
+        </is>
+      </c>
+      <c r="M12" s="41" t="n"/>
+      <c r="N12" s="41" t="inlineStr">
+        <is>
+          <t>pencairan/d52eb1b59daad7c10f3ac4f47758d9ce.png</t>
+        </is>
+      </c>
+      <c r="O12" s="41" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0005</t>
+        </is>
+      </c>
+      <c r="B13" s="42" t="inlineStr">
+        <is>
+          <t>AGT0011</t>
+        </is>
+      </c>
+      <c r="C13" s="42" t="inlineStr">
+        <is>
+          <t>SPHP 111</t>
+        </is>
+      </c>
+      <c r="D13" s="43" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="E13" s="44" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F13" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="42" t="inlineStr">
+        <is>
+          <t>mingguan</t>
+        </is>
+      </c>
+      <c r="H13" s="42" t="n">
+        <v>35</v>
+      </c>
+      <c r="I13" s="42" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="J13" s="44" t="n">
+        <v>112500</v>
+      </c>
+      <c r="K13" s="44" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="L13" s="42" t="inlineStr">
+        <is>
+          <t>aktif</t>
+        </is>
+      </c>
+      <c r="M13" s="41" t="n"/>
+      <c r="N13" s="41" t="inlineStr">
+        <is>
+          <t>pencairan/dcf01ec2c9dbbd96ec12046456f64311.png</t>
+        </is>
+      </c>
+      <c r="O13" s="41" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0004</t>
+        </is>
+      </c>
+      <c r="B14" s="42" t="inlineStr">
+        <is>
+          <t>AGT0012</t>
+        </is>
+      </c>
+      <c r="C14" s="42" t="inlineStr">
+        <is>
+          <t>SPHP 111</t>
+        </is>
+      </c>
+      <c r="D14" s="43" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="E14" s="44" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F14" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" s="42" t="inlineStr">
+        <is>
+          <t>mingguan</t>
+        </is>
+      </c>
+      <c r="H14" s="42" t="n">
+        <v>35</v>
+      </c>
+      <c r="I14" s="42" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="J14" s="44" t="n">
+        <v>112500</v>
+      </c>
+      <c r="K14" s="44" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="L14" s="42" t="inlineStr">
+        <is>
+          <t>aktif</t>
+        </is>
+      </c>
+      <c r="M14" s="41" t="n"/>
+      <c r="N14" s="41" t="inlineStr">
+        <is>
+          <t>pencairan/c5f4f844cb24e1c3f3396e58a0289f8a.png</t>
+        </is>
+      </c>
+      <c r="O14" s="41" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0003</t>
+        </is>
+      </c>
+      <c r="B15" s="42" t="inlineStr">
+        <is>
+          <t>AGT0013</t>
+        </is>
+      </c>
+      <c r="C15" s="42" t="inlineStr">
         <is>
           <t>SPHP 222</t>
         </is>
       </c>
-      <c r="D4" s="39" t="inlineStr">
-        <is>
-          <t>16/09/2026</t>
-        </is>
-      </c>
-      <c r="E4" s="39" t="n">
+      <c r="D15" s="43" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="E15" s="44" t="n">
         <v>2000000</v>
       </c>
-      <c r="F4" s="39" t="n">
+      <c r="F15" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="G4" s="39" t="inlineStr">
+      <c r="G15" s="42" t="inlineStr">
         <is>
           <t>mingguan</t>
         </is>
       </c>
-      <c r="H4" s="39" t="n">
+      <c r="H15" s="42" t="n">
         <v>35</v>
       </c>
-      <c r="I4" s="39" t="inlineStr">
+      <c r="I15" s="42" t="inlineStr">
         <is>
           <t>flat</t>
         </is>
       </c>
-      <c r="J4" s="39" t="n">
+      <c r="J15" s="44" t="n">
         <v>225000</v>
       </c>
-      <c r="K4" s="39" t="n">
+      <c r="K15" s="44" t="n">
         <v>2700000</v>
       </c>
-      <c r="L4" s="39" t="inlineStr">
+      <c r="L15" s="42" t="inlineStr">
         <is>
           <t>aktif</t>
         </is>
       </c>
-      <c r="M4" s="39" t="inlineStr"/>
-      <c r="N4" s="39" t="inlineStr">
-        <is>
-          <t>pencairan/54e9eecdb4bba08284c9bf990df993e6.jpg</t>
-        </is>
-      </c>
-      <c r="O4" s="39" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0011</t>
-        </is>
-      </c>
-      <c r="B5" s="39" t="inlineStr">
-        <is>
-          <t>AGT0018</t>
-        </is>
-      </c>
-      <c r="C5" s="39" t="inlineStr">
+      <c r="M15" s="41" t="n"/>
+      <c r="N15" s="41" t="inlineStr">
+        <is>
+          <t>pencairan/9af44ff189b009417b0a1c061b2f5b12.png</t>
+        </is>
+      </c>
+      <c r="O15" s="41" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0002</t>
+        </is>
+      </c>
+      <c r="B16" s="42" t="inlineStr">
+        <is>
+          <t>AGT0014</t>
+        </is>
+      </c>
+      <c r="C16" s="42" t="inlineStr">
+        <is>
+          <t>SPHP 222</t>
+        </is>
+      </c>
+      <c r="D16" s="43" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="E16" s="44" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="F16" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" s="42" t="inlineStr">
+        <is>
+          <t>mingguan</t>
+        </is>
+      </c>
+      <c r="H16" s="42" t="n">
+        <v>35</v>
+      </c>
+      <c r="I16" s="42" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="J16" s="44" t="n">
+        <v>225000</v>
+      </c>
+      <c r="K16" s="44" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="L16" s="42" t="inlineStr">
+        <is>
+          <t>aktif</t>
+        </is>
+      </c>
+      <c r="M16" s="41" t="n"/>
+      <c r="N16" s="41" t="inlineStr">
+        <is>
+          <t>pencairan/ac01f7ceee9f78c5b6597ce55af804c2.png</t>
+        </is>
+      </c>
+      <c r="O16" s="41" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261018-0016</t>
+        </is>
+      </c>
+      <c r="B17" s="42" t="inlineStr">
+        <is>
+          <t>AGTJ001</t>
+        </is>
+      </c>
+      <c r="C17" s="42" t="inlineStr">
+        <is>
+          <t>SPHPJ 3</t>
+        </is>
+      </c>
+      <c r="D17" s="43" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="E17" s="44" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="F17" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="42" t="inlineStr">
+        <is>
+          <t>bulanan</t>
+        </is>
+      </c>
+      <c r="H17" s="42" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="I17" s="42" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="J17" s="44" t="n">
+        <v>3530100</v>
+      </c>
+      <c r="K17" s="44" t="n">
+        <v>3530100</v>
+      </c>
+      <c r="L17" s="42" t="inlineStr">
+        <is>
+          <t>lunas</t>
+        </is>
+      </c>
+      <c r="M17" s="45" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="N17" s="41" t="inlineStr">
+        <is>
+          <t>pencairan/b666939db86fa61f7854dc0263c93dd7.jpg</t>
+        </is>
+      </c>
+      <c r="O17" s="41" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261020-0017</t>
+        </is>
+      </c>
+      <c r="B18" s="42" t="inlineStr">
+        <is>
+          <t>AGTJ002</t>
+        </is>
+      </c>
+      <c r="C18" s="42" t="inlineStr">
+        <is>
+          <t>SPHPJ 2</t>
+        </is>
+      </c>
+      <c r="D18" s="43" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="E18" s="44" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="F18" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="42" t="inlineStr">
+        <is>
+          <t>bulanan</t>
+        </is>
+      </c>
+      <c r="H18" s="42" t="n">
+        <v>21</v>
+      </c>
+      <c r="I18" s="42" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="J18" s="44" t="n">
+        <v>1210000</v>
+      </c>
+      <c r="K18" s="44" t="n">
+        <v>2420000</v>
+      </c>
+      <c r="L18" s="42" t="inlineStr">
+        <is>
+          <t>aktif</t>
+        </is>
+      </c>
+      <c r="M18" s="41" t="n"/>
+      <c r="N18" s="41" t="inlineStr">
+        <is>
+          <t>pencairan/ff475acbd828d89667090e73a71aa2a4.jpg</t>
+        </is>
+      </c>
+      <c r="O18" s="41" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261020-0018</t>
+        </is>
+      </c>
+      <c r="B19" s="42" t="inlineStr">
+        <is>
+          <t>AGT0006</t>
+        </is>
+      </c>
+      <c r="C19" s="42" t="inlineStr">
+        <is>
+          <t>SPHP 666</t>
+        </is>
+      </c>
+      <c r="D19" s="43" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="E19" s="44" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="F19" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="G19" s="42" t="inlineStr">
+        <is>
+          <t>dua_mingguan</t>
+        </is>
+      </c>
+      <c r="H19" s="42" t="n">
+        <v>45</v>
+      </c>
+      <c r="I19" s="42" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="J19" s="44" t="n">
+        <v>362500</v>
+      </c>
+      <c r="K19" s="44" t="n">
+        <v>4350000</v>
+      </c>
+      <c r="L19" s="42" t="inlineStr">
+        <is>
+          <t>aktif</t>
+        </is>
+      </c>
+      <c r="M19" s="41" t="n"/>
+      <c r="N19" s="41" t="inlineStr">
+        <is>
+          <t>pencairan/4522bd5d0f27124de52598518211c1e6.jpg</t>
+        </is>
+      </c>
+      <c r="O19" s="41" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261024-0020</t>
+        </is>
+      </c>
+      <c r="B20" s="42" t="inlineStr">
+        <is>
+          <t>AGT0020</t>
+        </is>
+      </c>
+      <c r="C20" s="42" t="inlineStr">
+        <is>
+          <t>SPHP 222</t>
+        </is>
+      </c>
+      <c r="D20" s="43" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+      <c r="E20" s="44" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="F20" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" s="42" t="inlineStr">
+        <is>
+          <t>mingguan</t>
+        </is>
+      </c>
+      <c r="H20" s="42" t="n">
+        <v>35</v>
+      </c>
+      <c r="I20" s="42" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="J20" s="44" t="n">
+        <v>225000</v>
+      </c>
+      <c r="K20" s="44" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="L20" s="42" t="inlineStr">
+        <is>
+          <t>aktif</t>
+        </is>
+      </c>
+      <c r="M20" s="41" t="n"/>
+      <c r="N20" s="41" t="inlineStr">
+        <is>
+          <t>pencairan/4e16516f5f2bb9d9308df3148118a02b.jpg</t>
+        </is>
+      </c>
+      <c r="O20" s="41" t="n"/>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="32">
+      <c r="A21" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261027-0024</t>
+        </is>
+      </c>
+      <c r="B21" s="42" t="inlineStr">
+        <is>
+          <t>AGT0022</t>
+        </is>
+      </c>
+      <c r="C21" s="42" t="inlineStr">
         <is>
           <t>SPHP 111</t>
         </is>
       </c>
-      <c r="D5" s="39" t="inlineStr">
-        <is>
-          <t>12/09/2026</t>
-        </is>
-      </c>
-      <c r="E5" s="39" t="n">
+      <c r="D21" s="43" t="inlineStr">
+        <is>
+          <t>27/10/2026</t>
+        </is>
+      </c>
+      <c r="E21" s="44" t="n">
         <v>1000000</v>
       </c>
-      <c r="F5" s="39" t="n">
+      <c r="F21" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="G5" s="39" t="inlineStr">
+      <c r="G21" s="42" t="inlineStr">
         <is>
           <t>mingguan</t>
         </is>
       </c>
-      <c r="H5" s="39" t="n">
+      <c r="H21" s="42" t="n">
         <v>35</v>
       </c>
-      <c r="I5" s="39" t="inlineStr">
+      <c r="I21" s="42" t="inlineStr">
         <is>
           <t>flat</t>
         </is>
       </c>
-      <c r="J5" s="39" t="n">
+      <c r="J21" s="44" t="n">
         <v>112500</v>
       </c>
-      <c r="K5" s="39" t="n">
+      <c r="K21" s="44" t="n">
         <v>1350000</v>
       </c>
-      <c r="L5" s="39" t="inlineStr">
+      <c r="L21" s="42" t="inlineStr">
         <is>
           <t>aktif</t>
         </is>
       </c>
-      <c r="M5" s="39" t="inlineStr"/>
-      <c r="N5" s="39" t="inlineStr">
-        <is>
-          <t>pencairan/2457c4049c3e0a6ff905afd679799931.png</t>
-        </is>
-      </c>
-      <c r="O5" s="39" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0010</t>
-        </is>
-      </c>
-      <c r="B6" s="39" t="inlineStr">
-        <is>
-          <t>AGT0006</t>
-        </is>
-      </c>
-      <c r="C6" s="39" t="inlineStr">
-        <is>
-          <t>SPHP 11</t>
-        </is>
-      </c>
-      <c r="D6" s="39" t="inlineStr">
-        <is>
-          <t>12/09/2026</t>
-        </is>
-      </c>
-      <c r="E6" s="39" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="F6" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" s="39" t="inlineStr">
-        <is>
-          <t>mingguan</t>
-        </is>
-      </c>
-      <c r="H6" s="39" t="n">
-        <v>25</v>
-      </c>
-      <c r="I6" s="39" t="inlineStr">
+      <c r="M21" s="41" t="n"/>
+      <c r="N21" s="41" t="inlineStr">
+        <is>
+          <t>pencairan/88041e5f2c3b491d150591f5327a0f3a.jpg</t>
+        </is>
+      </c>
+      <c r="O21" s="41" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261028-0025</t>
+        </is>
+      </c>
+      <c r="B22" s="42" t="inlineStr">
+        <is>
+          <t>AGT0021</t>
+        </is>
+      </c>
+      <c r="C22" s="42" t="inlineStr">
+        <is>
+          <t>SPHP 66</t>
+        </is>
+      </c>
+      <c r="D22" s="43" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="E22" s="44" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="F22" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="G22" s="42" t="inlineStr">
+        <is>
+          <t>dua_mingguan</t>
+        </is>
+      </c>
+      <c r="H22" s="42" t="n">
+        <v>45</v>
+      </c>
+      <c r="I22" s="42" t="inlineStr">
         <is>
           <t>flat</t>
         </is>
       </c>
-      <c r="J6" s="39" t="n">
-        <v>156250</v>
-      </c>
-      <c r="K6" s="39" t="n">
-        <v>1250000</v>
-      </c>
-      <c r="L6" s="39" t="inlineStr">
-        <is>
-          <t>lunas</t>
-        </is>
-      </c>
-      <c r="M6" s="39" t="inlineStr">
-        <is>
-          <t>17/10/2026</t>
-        </is>
-      </c>
-      <c r="N6" s="39" t="inlineStr">
-        <is>
-          <t>pencairan/d13534b7c79d70faa40a9b08d8d5f39d.png</t>
-        </is>
-      </c>
-      <c r="O6" s="39" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0014</t>
-        </is>
-      </c>
-      <c r="B7" s="39" t="inlineStr">
-        <is>
-          <t>AGT0015</t>
-        </is>
-      </c>
-      <c r="C7" s="39" t="inlineStr">
-        <is>
-          <t>SPHP 111</t>
-        </is>
-      </c>
-      <c r="D7" s="39" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-      <c r="E7" s="39" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="F7" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" s="39" t="inlineStr">
-        <is>
-          <t>mingguan</t>
-        </is>
-      </c>
-      <c r="H7" s="39" t="n">
-        <v>35</v>
-      </c>
-      <c r="I7" s="39" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="J7" s="39" t="n">
-        <v>112500</v>
-      </c>
-      <c r="K7" s="39" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="L7" s="39" t="inlineStr">
+      <c r="J22" s="44" t="n">
+        <v>241667</v>
+      </c>
+      <c r="K22" s="44" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="L22" s="42" t="inlineStr">
         <is>
           <t>aktif</t>
         </is>
       </c>
-      <c r="M7" s="39" t="inlineStr"/>
-      <c r="N7" s="39" t="inlineStr">
-        <is>
-          <t>pencairan/7e74657180eca4b8475a4044660b9a85.png</t>
-        </is>
-      </c>
-      <c r="O7" s="39" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0013</t>
-        </is>
-      </c>
-      <c r="B8" s="39" t="inlineStr">
-        <is>
-          <t>AGT0016</t>
-        </is>
-      </c>
-      <c r="C8" s="39" t="inlineStr">
-        <is>
-          <t>SPHP 111</t>
-        </is>
-      </c>
-      <c r="D8" s="39" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-      <c r="E8" s="39" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="F8" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="G8" s="39" t="inlineStr">
-        <is>
-          <t>mingguan</t>
-        </is>
-      </c>
-      <c r="H8" s="39" t="n">
-        <v>35</v>
-      </c>
-      <c r="I8" s="39" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="J8" s="39" t="n">
-        <v>112500</v>
-      </c>
-      <c r="K8" s="39" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="L8" s="39" t="inlineStr">
-        <is>
-          <t>aktif</t>
-        </is>
-      </c>
-      <c r="M8" s="39" t="inlineStr"/>
-      <c r="N8" s="39" t="inlineStr">
-        <is>
-          <t>pencairan/974ee4497315fc9a44fd1b207dd4605a.png</t>
-        </is>
-      </c>
-      <c r="O8" s="39" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0012</t>
-        </is>
-      </c>
-      <c r="B9" s="39" t="inlineStr">
-        <is>
-          <t>AGT0017</t>
-        </is>
-      </c>
-      <c r="C9" s="39" t="inlineStr">
-        <is>
-          <t>SPHP 111</t>
-        </is>
-      </c>
-      <c r="D9" s="39" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-      <c r="E9" s="39" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="F9" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" s="39" t="inlineStr">
-        <is>
-          <t>mingguan</t>
-        </is>
-      </c>
-      <c r="H9" s="39" t="n">
-        <v>35</v>
-      </c>
-      <c r="I9" s="39" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="J9" s="39" t="n">
-        <v>112500</v>
-      </c>
-      <c r="K9" s="39" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="L9" s="39" t="inlineStr">
-        <is>
-          <t>aktif</t>
-        </is>
-      </c>
-      <c r="M9" s="39" t="inlineStr"/>
-      <c r="N9" s="39" t="inlineStr">
-        <is>
-          <t>pencairan/deb64ae0b0ff2718b1786b9142a2f5c7.png</t>
-        </is>
-      </c>
-      <c r="O9" s="39" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0008</t>
-        </is>
-      </c>
-      <c r="B10" s="39" t="inlineStr">
-        <is>
-          <t>AGT0008</t>
-        </is>
-      </c>
-      <c r="C10" s="39" t="inlineStr">
-        <is>
-          <t>SPHP 111</t>
-        </is>
-      </c>
-      <c r="D10" s="39" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="E10" s="39" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="F10" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="G10" s="39" t="inlineStr">
-        <is>
-          <t>mingguan</t>
-        </is>
-      </c>
-      <c r="H10" s="39" t="n">
-        <v>35</v>
-      </c>
-      <c r="I10" s="39" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="J10" s="39" t="n">
-        <v>112500</v>
-      </c>
-      <c r="K10" s="39" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="L10" s="39" t="inlineStr">
-        <is>
-          <t>aktif</t>
-        </is>
-      </c>
-      <c r="M10" s="39" t="inlineStr"/>
-      <c r="N10" s="39" t="inlineStr">
-        <is>
-          <t>pencairan/17864ddf79fc06d7c95b368255bcca73.png</t>
-        </is>
-      </c>
-      <c r="O10" s="39" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0007</t>
-        </is>
-      </c>
-      <c r="B11" s="39" t="inlineStr">
-        <is>
-          <t>AGT0009</t>
-        </is>
-      </c>
-      <c r="C11" s="39" t="inlineStr">
-        <is>
-          <t>SPHP 111</t>
-        </is>
-      </c>
-      <c r="D11" s="39" t="inlineStr">
-        <is>
-          <t>18/09/2026</t>
-        </is>
-      </c>
-      <c r="E11" s="39" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="F11" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" s="39" t="inlineStr">
-        <is>
-          <t>mingguan</t>
-        </is>
-      </c>
-      <c r="H11" s="39" t="n">
-        <v>35</v>
-      </c>
-      <c r="I11" s="39" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="J11" s="39" t="n">
-        <v>112500</v>
-      </c>
-      <c r="K11" s="39" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="L11" s="39" t="inlineStr">
-        <is>
-          <t>aktif</t>
-        </is>
-      </c>
-      <c r="M11" s="39" t="inlineStr"/>
-      <c r="N11" s="39" t="inlineStr">
-        <is>
-          <t>pencairan/c8976ddcde2e1ab8d107de82965cac32.png</t>
-        </is>
-      </c>
-      <c r="O11" s="39" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0006</t>
-        </is>
-      </c>
-      <c r="B12" s="39" t="inlineStr">
-        <is>
-          <t>AGT0010</t>
-        </is>
-      </c>
-      <c r="C12" s="39" t="inlineStr">
-        <is>
-          <t>SPHP 111</t>
-        </is>
-      </c>
-      <c r="D12" s="39" t="inlineStr">
-        <is>
-          <t>25/09/2026</t>
-        </is>
-      </c>
-      <c r="E12" s="39" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="F12" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="G12" s="39" t="inlineStr">
-        <is>
-          <t>mingguan</t>
-        </is>
-      </c>
-      <c r="H12" s="39" t="n">
-        <v>35</v>
-      </c>
-      <c r="I12" s="39" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="J12" s="39" t="n">
-        <v>112500</v>
-      </c>
-      <c r="K12" s="39" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="L12" s="39" t="inlineStr">
-        <is>
-          <t>aktif</t>
-        </is>
-      </c>
-      <c r="M12" s="39" t="inlineStr"/>
-      <c r="N12" s="39" t="inlineStr">
-        <is>
-          <t>pencairan/d52eb1b59daad7c10f3ac4f47758d9ce.png</t>
-        </is>
-      </c>
-      <c r="O12" s="39" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0005</t>
-        </is>
-      </c>
-      <c r="B13" s="39" t="inlineStr">
-        <is>
-          <t>AGT0011</t>
-        </is>
-      </c>
-      <c r="C13" s="39" t="inlineStr">
-        <is>
-          <t>SPHP 111</t>
-        </is>
-      </c>
-      <c r="D13" s="39" t="inlineStr">
-        <is>
-          <t>28/09/2026</t>
-        </is>
-      </c>
-      <c r="E13" s="39" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="F13" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" s="39" t="inlineStr">
-        <is>
-          <t>mingguan</t>
-        </is>
-      </c>
-      <c r="H13" s="39" t="n">
-        <v>35</v>
-      </c>
-      <c r="I13" s="39" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="J13" s="39" t="n">
-        <v>112500</v>
-      </c>
-      <c r="K13" s="39" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="L13" s="39" t="inlineStr">
-        <is>
-          <t>aktif</t>
-        </is>
-      </c>
-      <c r="M13" s="39" t="inlineStr"/>
-      <c r="N13" s="39" t="inlineStr">
-        <is>
-          <t>pencairan/dcf01ec2c9dbbd96ec12046456f64311.png</t>
-        </is>
-      </c>
-      <c r="O13" s="39" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0004</t>
-        </is>
-      </c>
-      <c r="B14" s="39" t="inlineStr">
-        <is>
-          <t>AGT0012</t>
-        </is>
-      </c>
-      <c r="C14" s="39" t="inlineStr">
-        <is>
-          <t>SPHP 111</t>
-        </is>
-      </c>
-      <c r="D14" s="39" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
-      <c r="E14" s="39" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="F14" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="G14" s="39" t="inlineStr">
-        <is>
-          <t>mingguan</t>
-        </is>
-      </c>
-      <c r="H14" s="39" t="n">
-        <v>35</v>
-      </c>
-      <c r="I14" s="39" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="J14" s="39" t="n">
-        <v>112500</v>
-      </c>
-      <c r="K14" s="39" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="L14" s="39" t="inlineStr">
-        <is>
-          <t>aktif</t>
-        </is>
-      </c>
-      <c r="M14" s="39" t="inlineStr"/>
-      <c r="N14" s="39" t="inlineStr">
-        <is>
-          <t>pencairan/c5f4f844cb24e1c3f3396e58a0289f8a.png</t>
-        </is>
-      </c>
-      <c r="O14" s="39" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0003</t>
-        </is>
-      </c>
-      <c r="B15" s="39" t="inlineStr">
-        <is>
-          <t>AGT0013</t>
-        </is>
-      </c>
-      <c r="C15" s="39" t="inlineStr">
-        <is>
-          <t>SPHP 222</t>
-        </is>
-      </c>
-      <c r="D15" s="39" t="inlineStr">
-        <is>
-          <t>08/10/2026</t>
-        </is>
-      </c>
-      <c r="E15" s="39" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="F15" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" s="39" t="inlineStr">
-        <is>
-          <t>mingguan</t>
-        </is>
-      </c>
-      <c r="H15" s="39" t="n">
-        <v>35</v>
-      </c>
-      <c r="I15" s="39" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="J15" s="39" t="n">
-        <v>225000</v>
-      </c>
-      <c r="K15" s="39" t="n">
-        <v>2700000</v>
-      </c>
-      <c r="L15" s="39" t="inlineStr">
-        <is>
-          <t>aktif</t>
-        </is>
-      </c>
-      <c r="M15" s="39" t="inlineStr"/>
-      <c r="N15" s="39" t="inlineStr">
-        <is>
-          <t>pencairan/9af44ff189b009417b0a1c061b2f5b12.png</t>
-        </is>
-      </c>
-      <c r="O15" s="39" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0002</t>
-        </is>
-      </c>
-      <c r="B16" s="39" t="inlineStr">
-        <is>
-          <t>AGT0014</t>
-        </is>
-      </c>
-      <c r="C16" s="39" t="inlineStr">
-        <is>
-          <t>SPHP 222</t>
-        </is>
-      </c>
-      <c r="D16" s="39" t="inlineStr">
-        <is>
-          <t>12/10/2026</t>
-        </is>
-      </c>
-      <c r="E16" s="39" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="F16" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="G16" s="39" t="inlineStr">
-        <is>
-          <t>mingguan</t>
-        </is>
-      </c>
-      <c r="H16" s="39" t="n">
-        <v>35</v>
-      </c>
-      <c r="I16" s="39" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="J16" s="39" t="n">
-        <v>225000</v>
-      </c>
-      <c r="K16" s="39" t="n">
-        <v>2700000</v>
-      </c>
-      <c r="L16" s="39" t="inlineStr">
-        <is>
-          <t>aktif</t>
-        </is>
-      </c>
-      <c r="M16" s="39" t="inlineStr"/>
-      <c r="N16" s="39" t="inlineStr">
-        <is>
-          <t>pencairan/ac01f7ceee9f78c5b6597ce55af804c2.png</t>
-        </is>
-      </c>
-      <c r="O16" s="39" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261018-0015</t>
-        </is>
-      </c>
-      <c r="B17" s="39" t="inlineStr">
-        <is>
-          <t>AGTJ001</t>
-        </is>
-      </c>
-      <c r="C17" s="39" t="inlineStr">
-        <is>
-          <t>SPHPJ 3</t>
-        </is>
-      </c>
-      <c r="D17" s="39" t="inlineStr">
-        <is>
-          <t>18/10/2026</t>
-        </is>
-      </c>
-      <c r="E17" s="39" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="F17" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="39" t="inlineStr">
-        <is>
-          <t>bulanan</t>
-        </is>
-      </c>
-      <c r="H17" s="39" t="n">
-        <v>17.67</v>
-      </c>
-      <c r="I17" s="39" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="J17" s="39" t="n">
-        <v>3530100</v>
-      </c>
-      <c r="K17" s="39" t="n">
-        <v>3530100</v>
-      </c>
-      <c r="L17" s="39" t="inlineStr">
-        <is>
-          <t>lunas</t>
-        </is>
-      </c>
-      <c r="M17" s="39" t="inlineStr">
-        <is>
-          <t>18/10/2026</t>
-        </is>
-      </c>
-      <c r="N17" s="39" t="inlineStr">
-        <is>
-          <t>pencairan/2fb0a07aef780be364982a97357385c4.png</t>
-        </is>
-      </c>
-      <c r="O17" s="39" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261018-0016</t>
-        </is>
-      </c>
-      <c r="B18" s="39" t="inlineStr">
-        <is>
-          <t>AGTJ001</t>
-        </is>
-      </c>
-      <c r="C18" s="39" t="inlineStr">
-        <is>
-          <t>SPHPJ 3</t>
-        </is>
-      </c>
-      <c r="D18" s="39" t="inlineStr">
-        <is>
-          <t>12/10/2026</t>
-        </is>
-      </c>
-      <c r="E18" s="39" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="F18" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="39" t="inlineStr">
-        <is>
-          <t>bulanan</t>
-        </is>
-      </c>
-      <c r="H18" s="39" t="n">
-        <v>17.67</v>
-      </c>
-      <c r="I18" s="39" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="J18" s="39" t="n">
-        <v>3530100</v>
-      </c>
-      <c r="K18" s="39" t="n">
-        <v>3530100</v>
-      </c>
-      <c r="L18" s="39" t="inlineStr">
-        <is>
-          <t>lunas</t>
-        </is>
-      </c>
-      <c r="M18" s="39" t="inlineStr">
-        <is>
-          <t>23/10/2026</t>
-        </is>
-      </c>
-      <c r="N18" s="39" t="inlineStr">
-        <is>
-          <t>pencairan/b666939db86fa61f7854dc0263c93dd7.jpg</t>
-        </is>
-      </c>
-      <c r="O18" s="39" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261020-0017</t>
-        </is>
-      </c>
-      <c r="B19" s="39" t="inlineStr">
-        <is>
-          <t>AGTJ002</t>
-        </is>
-      </c>
-      <c r="C19" s="39" t="inlineStr">
-        <is>
-          <t>SPHPJ 2</t>
-        </is>
-      </c>
-      <c r="D19" s="39" t="inlineStr">
-        <is>
-          <t>20/10/2026</t>
-        </is>
-      </c>
-      <c r="E19" s="39" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="F19" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="G19" s="39" t="inlineStr">
-        <is>
-          <t>bulanan</t>
-        </is>
-      </c>
-      <c r="H19" s="39" t="n">
-        <v>21</v>
-      </c>
-      <c r="I19" s="39" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="J19" s="39" t="n">
-        <v>1210000</v>
-      </c>
-      <c r="K19" s="39" t="n">
-        <v>2420000</v>
-      </c>
-      <c r="L19" s="39" t="inlineStr">
-        <is>
-          <t>aktif</t>
-        </is>
-      </c>
-      <c r="M19" s="39" t="inlineStr"/>
-      <c r="N19" s="39" t="inlineStr">
-        <is>
-          <t>pencairan/ff475acbd828d89667090e73a71aa2a4.jpg</t>
-        </is>
-      </c>
-      <c r="O19" s="39" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261020-0018</t>
-        </is>
-      </c>
-      <c r="B20" s="39" t="inlineStr">
-        <is>
-          <t>AGT0006</t>
-        </is>
-      </c>
-      <c r="C20" s="39" t="inlineStr">
-        <is>
-          <t>SPHP 666</t>
-        </is>
-      </c>
-      <c r="D20" s="39" t="inlineStr">
-        <is>
-          <t>20/10/2026</t>
-        </is>
-      </c>
-      <c r="E20" s="39" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="F20" s="39" t="n">
-        <v>6</v>
-      </c>
-      <c r="G20" s="39" t="inlineStr">
-        <is>
-          <t>dua_mingguan</t>
-        </is>
-      </c>
-      <c r="H20" s="39" t="n">
-        <v>45</v>
-      </c>
-      <c r="I20" s="39" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="J20" s="39" t="n">
-        <v>362500</v>
-      </c>
-      <c r="K20" s="39" t="n">
-        <v>4350000</v>
-      </c>
-      <c r="L20" s="39" t="inlineStr">
-        <is>
-          <t>aktif</t>
-        </is>
-      </c>
-      <c r="M20" s="39" t="inlineStr"/>
-      <c r="N20" s="39" t="inlineStr">
-        <is>
-          <t>pencairan/4522bd5d0f27124de52598518211c1e6.jpg</t>
-        </is>
-      </c>
-      <c r="O20" s="39" t="inlineStr"/>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="32">
-      <c r="A21" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261024-0020</t>
-        </is>
-      </c>
-      <c r="B21" s="39" t="inlineStr">
-        <is>
-          <t>AGT0020</t>
-        </is>
-      </c>
-      <c r="C21" s="39" t="inlineStr">
-        <is>
-          <t>SPHP 222</t>
-        </is>
-      </c>
-      <c r="D21" s="39" t="inlineStr">
-        <is>
-          <t>24/10/2026</t>
-        </is>
-      </c>
-      <c r="E21" s="39" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="F21" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="G21" s="39" t="inlineStr">
-        <is>
-          <t>mingguan</t>
-        </is>
-      </c>
-      <c r="H21" s="39" t="n">
-        <v>35</v>
-      </c>
-      <c r="I21" s="39" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="J21" s="39" t="n">
-        <v>225000</v>
-      </c>
-      <c r="K21" s="39" t="n">
-        <v>2700000</v>
-      </c>
-      <c r="L21" s="39" t="inlineStr">
-        <is>
-          <t>aktif</t>
-        </is>
-      </c>
-      <c r="M21" s="39" t="inlineStr"/>
-      <c r="N21" s="39" t="inlineStr">
-        <is>
-          <t>pencairan/4e16516f5f2bb9d9308df3148118a02b.jpg</t>
-        </is>
-      </c>
-      <c r="O21" s="39" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261024-0021</t>
-        </is>
-      </c>
-      <c r="B22" s="39" t="inlineStr">
-        <is>
-          <t>AGT0021</t>
-        </is>
-      </c>
-      <c r="C22" s="39" t="inlineStr">
-        <is>
-          <t>SPHP 66</t>
-        </is>
-      </c>
-      <c r="D22" s="39" t="inlineStr">
-        <is>
-          <t>24/10/2026</t>
-        </is>
-      </c>
-      <c r="E22" s="39" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="F22" s="39" t="n">
-        <v>6</v>
-      </c>
-      <c r="G22" s="39" t="inlineStr">
-        <is>
-          <t>dua_mingguan</t>
-        </is>
-      </c>
-      <c r="H22" s="39" t="n">
-        <v>45</v>
-      </c>
-      <c r="I22" s="39" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="J22" s="39" t="n">
-        <v>241667</v>
-      </c>
-      <c r="K22" s="39" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="L22" s="39" t="inlineStr">
-        <is>
-          <t>lunas</t>
-        </is>
-      </c>
-      <c r="M22" s="39" t="inlineStr">
-        <is>
-          <t>26/10/2026</t>
-        </is>
-      </c>
-      <c r="N22" s="39" t="inlineStr">
-        <is>
-          <t>pencairan/f30cbb129236d9be4c923eeb7beeeb59.jpg</t>
-        </is>
-      </c>
-      <c r="O22" s="39" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261026-0023</t>
-        </is>
-      </c>
-      <c r="B23" s="39" t="inlineStr">
-        <is>
-          <t>AGT0021</t>
-        </is>
-      </c>
-      <c r="C23" s="39" t="inlineStr">
-        <is>
-          <t>SPHP 1</t>
-        </is>
-      </c>
-      <c r="D23" s="39" t="inlineStr">
-        <is>
-          <t>26/10/2026</t>
-        </is>
-      </c>
-      <c r="E23" s="39" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="F23" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="39" t="inlineStr">
-        <is>
-          <t>mingguan</t>
-        </is>
-      </c>
-      <c r="H23" s="39" t="n">
-        <v>15</v>
-      </c>
-      <c r="I23" s="39" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="J23" s="39" t="n">
-        <v>287500</v>
-      </c>
-      <c r="K23" s="39" t="n">
-        <v>1150000</v>
-      </c>
-      <c r="L23" s="39" t="inlineStr">
-        <is>
-          <t>lunas</t>
-        </is>
-      </c>
-      <c r="M23" s="39" t="inlineStr">
-        <is>
-          <t>27/10/2026</t>
-        </is>
-      </c>
-      <c r="N23" s="39" t="inlineStr">
-        <is>
-          <t>pencairan/bbc831df5dd3663c71e7c40be95d2b76.png</t>
-        </is>
-      </c>
-      <c r="O23" s="39" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261027-0024</t>
-        </is>
-      </c>
-      <c r="B24" s="39" t="inlineStr">
-        <is>
-          <t>AGT0022</t>
-        </is>
-      </c>
-      <c r="C24" s="39" t="inlineStr">
-        <is>
-          <t>SPHP 111</t>
-        </is>
-      </c>
-      <c r="D24" s="39" t="inlineStr">
-        <is>
-          <t>27/10/2026</t>
-        </is>
-      </c>
-      <c r="E24" s="39" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="F24" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="G24" s="39" t="inlineStr">
-        <is>
-          <t>mingguan</t>
-        </is>
-      </c>
-      <c r="H24" s="39" t="n">
-        <v>35</v>
-      </c>
-      <c r="I24" s="39" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="J24" s="39" t="n">
-        <v>112500</v>
-      </c>
-      <c r="K24" s="39" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="L24" s="39" t="inlineStr">
-        <is>
-          <t>aktif</t>
-        </is>
-      </c>
-      <c r="M24" s="39" t="inlineStr"/>
-      <c r="N24" s="39" t="inlineStr">
-        <is>
-          <t>pencairan/88041e5f2c3b491d150591f5327a0f3a.jpg</t>
-        </is>
-      </c>
-      <c r="O24" s="39" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261028-0025</t>
-        </is>
-      </c>
-      <c r="B25" s="39" t="inlineStr">
-        <is>
-          <t>AGT0021</t>
-        </is>
-      </c>
-      <c r="C25" s="39" t="inlineStr">
-        <is>
-          <t>SPHP 66</t>
-        </is>
-      </c>
-      <c r="D25" s="39" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="E25" s="39" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="F25" s="39" t="n">
-        <v>6</v>
-      </c>
-      <c r="G25" s="39" t="inlineStr">
-        <is>
-          <t>dua_mingguan</t>
-        </is>
-      </c>
-      <c r="H25" s="39" t="n">
-        <v>45</v>
-      </c>
-      <c r="I25" s="39" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="J25" s="39" t="n">
-        <v>241667</v>
-      </c>
-      <c r="K25" s="39" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="L25" s="39" t="inlineStr">
-        <is>
-          <t>aktif</t>
-        </is>
-      </c>
-      <c r="M25" s="39" t="inlineStr"/>
-      <c r="N25" s="39" t="inlineStr">
+      <c r="M22" s="41" t="n"/>
+      <c r="N22" s="41" t="inlineStr">
         <is>
           <t>pencairan/4b5f4898399d748a0da3fdafbe9ddd03.jpg</t>
         </is>
       </c>
-      <c r="O25" s="39" t="inlineStr"/>
+      <c r="O22" s="41" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N1000"/>
+  <autoFilter ref="A2:O22"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -4174,7 +4162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col width="18" customWidth="1" style="32" min="1" max="1"/>
@@ -4196,1004 +4184,1229 @@
       </c>
     </row>
     <row r="2" ht="34" customHeight="1" s="32">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="38" t="inlineStr">
         <is>
           <t>ID Pembayaran</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="38" t="inlineStr">
         <is>
           <t>ID Pinjaman Lama*</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="38" t="inlineStr">
         <is>
           <t>Tanggal Bayar*</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="38" t="inlineStr">
         <is>
           <t>Angsuran Ke</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" s="38" t="inlineStr">
         <is>
           <t>Jenis Pembayaran*</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="38" t="inlineStr">
         <is>
           <t>Pokok (Rp)</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" s="38" t="inlineStr">
         <is>
           <t>Bunga (Rp)</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" s="38" t="inlineStr">
         <is>
           <t>Denda (Rp)</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="I2" s="38" t="inlineStr">
         <is>
           <t>Total Diterima (Rp)*</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="J2" s="38" t="inlineStr">
         <is>
           <t>Status*</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="K2" s="38" t="inlineStr">
         <is>
           <t>Keterangan</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1" s="32">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
+        <is>
+          <t>BYR-20260925-SOLIKAH-D</t>
+        </is>
+      </c>
+      <c r="B3" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0007</t>
+        </is>
+      </c>
+      <c r="C3" s="43" t="n">
+        <v>46290</v>
+      </c>
+      <c r="D3" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="42" t="inlineStr">
+        <is>
+          <t>cicilan</t>
+        </is>
+      </c>
+      <c r="F3" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="46" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I3" s="44" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J3" s="42" t="inlineStr">
+        <is>
+          <t>dibayar</t>
+        </is>
+      </c>
+      <c r="K3" s="41" t="inlineStr">
+        <is>
+          <t>DENDA 1.500 Solikah tgl 25/09/2026 — wajib muncul di Laporan Denda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1" s="32">
+      <c r="A4" s="41" t="inlineStr">
+        <is>
+          <t>BYR-20260915-002</t>
+        </is>
+      </c>
+      <c r="B4" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0002</t>
+        </is>
+      </c>
+      <c r="C4" s="43" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="D4" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="42" t="inlineStr">
+        <is>
+          <t>cicilan</t>
+        </is>
+      </c>
+      <c r="F4" s="46" t="n">
+        <v>166667</v>
+      </c>
+      <c r="G4" s="46" t="n">
+        <v>58333</v>
+      </c>
+      <c r="H4" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="44" t="n">
+        <v>225000</v>
+      </c>
+      <c r="J4" s="42" t="inlineStr">
+        <is>
+          <t>dibayar</t>
+        </is>
+      </c>
+      <c r="K4" s="41" t="inlineStr">
+        <is>
+          <t>angsuran mingguan ke-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1" s="32">
+      <c r="A5" s="41" t="inlineStr">
+        <is>
+          <t>BYR-20260915-010</t>
+        </is>
+      </c>
+      <c r="B5" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0010</t>
+        </is>
+      </c>
+      <c r="C5" s="43" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="D5" s="41" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="42" t="inlineStr">
+        <is>
+          <t>cicilan</t>
+        </is>
+      </c>
+      <c r="F5" s="46" t="n">
+        <v>125000</v>
+      </c>
+      <c r="G5" s="46" t="n">
+        <v>31250</v>
+      </c>
+      <c r="H5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="44" t="n">
+        <v>625000</v>
+      </c>
+      <c r="J5" s="42" t="inlineStr">
+        <is>
+          <t>dibayar</t>
+        </is>
+      </c>
+      <c r="K5" s="41" t="inlineStr">
+        <is>
+          <t>angsuran mingguan ke-4 ke 5nya pelunasan</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="32">
+      <c r="A6" s="41" t="inlineStr">
+        <is>
+          <t>BYR-20261015-MASLUKAH-D</t>
+        </is>
+      </c>
+      <c r="B6" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0008</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="n">
+        <v>46310</v>
+      </c>
+      <c r="D6" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="42" t="inlineStr">
+        <is>
+          <t>cicilan</t>
+        </is>
+      </c>
+      <c r="F6" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="46" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I6" s="44" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J6" s="42" t="inlineStr">
+        <is>
+          <t>dibayar</t>
+        </is>
+      </c>
+      <c r="K6" s="41" t="inlineStr">
+        <is>
+          <t>DENDA 1.500 Maslukah tgl 15/10/2026 — wajib muncul di Laporan Denda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1" s="32" thickBot="1">
+      <c r="A7" s="41" t="inlineStr">
+        <is>
+          <t>BYR-20260915-007</t>
+        </is>
+      </c>
+      <c r="B7" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0007</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="D7" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="42" t="inlineStr">
+        <is>
+          <t>cicilan</t>
+        </is>
+      </c>
+      <c r="F7" s="46" t="n">
+        <v>83333</v>
+      </c>
+      <c r="G7" s="46" t="n">
+        <v>29167</v>
+      </c>
+      <c r="H7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="44" t="n">
+        <v>337500</v>
+      </c>
+      <c r="J7" s="42" t="inlineStr">
+        <is>
+          <t>dibayar</t>
+        </is>
+      </c>
+      <c r="K7" s="41" t="inlineStr">
+        <is>
+          <t>angsuran mingguan ke-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="32">
+      <c r="A8" s="41" t="inlineStr">
+        <is>
+          <t>BYR-20260915-015</t>
+        </is>
+      </c>
+      <c r="B8" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0010</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="D8" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="42" t="inlineStr">
+        <is>
+          <t>pelunasan</t>
+        </is>
+      </c>
+      <c r="F8" s="46" t="n">
+        <v>125000</v>
+      </c>
+      <c r="G8" s="46" t="n">
+        <v>31250</v>
+      </c>
+      <c r="H8" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="44" t="n">
+        <v>625000</v>
+      </c>
+      <c r="J8" s="42" t="inlineStr">
+        <is>
+          <t>dibayar</t>
+        </is>
+      </c>
+      <c r="K8" s="41" t="inlineStr">
+        <is>
+          <t>Pelunasan; ID diperbaiki karena duplikat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="32">
+      <c r="A9" s="41" t="inlineStr">
+        <is>
+          <t>BYR-20260915-003</t>
+        </is>
+      </c>
+      <c r="B9" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0003</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>21/10/2026</t>
+        </is>
+      </c>
+      <c r="D9" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="42" t="inlineStr">
+        <is>
+          <t>cicilan</t>
+        </is>
+      </c>
+      <c r="F9" s="46" t="n">
+        <v>166667</v>
+      </c>
+      <c r="G9" s="46" t="n">
+        <v>58333</v>
+      </c>
+      <c r="H9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="44" t="n">
+        <v>1125000</v>
+      </c>
+      <c r="J9" s="42" t="inlineStr">
+        <is>
+          <t>dibayar</t>
+        </is>
+      </c>
+      <c r="K9" s="41" t="inlineStr">
+        <is>
+          <t>angsuran mingguan ke-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="32">
+      <c r="A10" s="41" t="inlineStr">
+        <is>
+          <t>BYR-20260915-008</t>
+        </is>
+      </c>
+      <c r="B10" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0008</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="inlineStr">
+        <is>
+          <t>21/10/2026</t>
+        </is>
+      </c>
+      <c r="D10" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="42" t="inlineStr">
+        <is>
+          <t>cicilan</t>
+        </is>
+      </c>
+      <c r="F10" s="46" t="n">
+        <v>83333</v>
+      </c>
+      <c r="G10" s="46" t="n">
+        <v>29167</v>
+      </c>
+      <c r="H10" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="44" t="n">
+        <v>337500</v>
+      </c>
+      <c r="J10" s="42" t="inlineStr">
+        <is>
+          <t>dibayar</t>
+        </is>
+      </c>
+      <c r="K10" s="41" t="inlineStr">
+        <is>
+          <t>angsuran mingguan ke-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1" s="32">
+      <c r="A11" s="41" t="inlineStr">
         <is>
           <t>BYR-20260915-001</t>
         </is>
       </c>
-      <c r="B3" s="39" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>PJN-20261013-0001</t>
         </is>
       </c>
-      <c r="C3" s="39" t="inlineStr">
+      <c r="C11" s="43" t="inlineStr">
         <is>
           <t>22/10/2026</t>
         </is>
       </c>
-      <c r="D3" s="39" t="n">
+      <c r="D11" s="41" t="n">
         <v>6</v>
       </c>
-      <c r="E3" s="39" t="inlineStr">
+      <c r="E11" s="42" t="inlineStr">
         <is>
           <t>cicilan</t>
         </is>
       </c>
-      <c r="F3" s="39" t="n">
+      <c r="F11" s="46" t="n">
         <v>166667</v>
       </c>
-      <c r="G3" s="39" t="n">
+      <c r="G11" s="46" t="n">
         <v>58333</v>
       </c>
-      <c r="H3" s="39" t="n">
+      <c r="H11" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="39" t="n">
+      <c r="I11" s="44" t="n">
         <v>1332000</v>
       </c>
-      <c r="J3" s="39" t="inlineStr">
+      <c r="J11" s="42" t="inlineStr">
         <is>
           <t>dibayar</t>
         </is>
       </c>
-      <c r="K3" s="39" t="inlineStr">
+      <c r="K11" s="41" t="inlineStr">
         <is>
           <t>angsuran mingguan ke-6</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1" s="32">
-      <c r="A4" s="39" t="inlineStr">
-        <is>
-          <t>BYR-20260915-002</t>
-        </is>
-      </c>
-      <c r="B4" s="39" t="inlineStr">
+    <row r="12" ht="30" customHeight="1" s="32">
+      <c r="A12" s="41" t="inlineStr">
+        <is>
+          <t>BYR-20260915-004</t>
+        </is>
+      </c>
+      <c r="B12" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0004</t>
+        </is>
+      </c>
+      <c r="C12" s="43" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="D12" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="42" t="inlineStr">
+        <is>
+          <t>cicilan</t>
+        </is>
+      </c>
+      <c r="F12" s="46" t="n">
+        <v>83333</v>
+      </c>
+      <c r="G12" s="46" t="n">
+        <v>29167</v>
+      </c>
+      <c r="H12" s="46" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I12" s="44" t="n">
+        <v>562500</v>
+      </c>
+      <c r="J12" s="42" t="inlineStr">
+        <is>
+          <t>dibayar</t>
+        </is>
+      </c>
+      <c r="K12" s="41" t="inlineStr">
+        <is>
+          <t>angsuran mingguan ke-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="32">
+      <c r="A13" s="41" t="inlineStr">
+        <is>
+          <t>BYR-20260915-009</t>
+        </is>
+      </c>
+      <c r="B13" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0009</t>
+        </is>
+      </c>
+      <c r="C13" s="43" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="D13" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="42" t="inlineStr">
+        <is>
+          <t>cicilan</t>
+        </is>
+      </c>
+      <c r="F13" s="46" t="n">
+        <v>166667</v>
+      </c>
+      <c r="G13" s="46" t="n">
+        <v>58333</v>
+      </c>
+      <c r="H13" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="44" t="n">
+        <v>450000</v>
+      </c>
+      <c r="J13" s="42" t="inlineStr">
+        <is>
+          <t>dibayar</t>
+        </is>
+      </c>
+      <c r="K13" s="41" t="inlineStr">
+        <is>
+          <t>angsuran mingguan ke-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="32">
+      <c r="A14" s="41" t="inlineStr">
+        <is>
+          <t>BYR-20260915-011</t>
+        </is>
+      </c>
+      <c r="B14" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0011</t>
+        </is>
+      </c>
+      <c r="C14" s="43" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="D14" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" s="42" t="inlineStr">
+        <is>
+          <t>cicilan</t>
+        </is>
+      </c>
+      <c r="F14" s="46" t="n">
+        <v>83333</v>
+      </c>
+      <c r="G14" s="46" t="n">
+        <v>29167</v>
+      </c>
+      <c r="H14" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="44" t="n">
+        <v>675000</v>
+      </c>
+      <c r="J14" s="42" t="inlineStr">
+        <is>
+          <t>dibayar</t>
+        </is>
+      </c>
+      <c r="K14" s="41" t="inlineStr">
+        <is>
+          <t>angsuran mingguan ke-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="32">
+      <c r="A15" s="41" t="inlineStr">
+        <is>
+          <t>BYR-20260915-012</t>
+        </is>
+      </c>
+      <c r="B15" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0012</t>
+        </is>
+      </c>
+      <c r="C15" s="43" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="D15" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" s="42" t="inlineStr">
+        <is>
+          <t>cicilan</t>
+        </is>
+      </c>
+      <c r="F15" s="46" t="n">
+        <v>83333</v>
+      </c>
+      <c r="G15" s="46" t="n">
+        <v>29167</v>
+      </c>
+      <c r="H15" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="44" t="n">
+        <v>675000</v>
+      </c>
+      <c r="J15" s="42" t="inlineStr">
+        <is>
+          <t>dibayar</t>
+        </is>
+      </c>
+      <c r="K15" s="41" t="inlineStr">
+        <is>
+          <t>angsuran mingguan ke-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="32" thickBot="1">
+      <c r="A16" s="41" t="inlineStr">
+        <is>
+          <t>BYR-20260915-013</t>
+        </is>
+      </c>
+      <c r="B16" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0013</t>
+        </is>
+      </c>
+      <c r="C16" s="43" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="D16" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" s="42" t="inlineStr">
+        <is>
+          <t>cicilan</t>
+        </is>
+      </c>
+      <c r="F16" s="46" t="n">
+        <v>83333</v>
+      </c>
+      <c r="G16" s="46" t="n">
+        <v>29167</v>
+      </c>
+      <c r="H16" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="44" t="n">
+        <v>675000</v>
+      </c>
+      <c r="J16" s="42" t="inlineStr">
+        <is>
+          <t>dibayar</t>
+        </is>
+      </c>
+      <c r="K16" s="41" t="inlineStr">
+        <is>
+          <t>angsuran mingguan ke-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="41" t="inlineStr">
+        <is>
+          <t>BYR-20260915-005</t>
+        </is>
+      </c>
+      <c r="B17" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0005</t>
+        </is>
+      </c>
+      <c r="C17" s="43" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="D17" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" s="42" t="inlineStr">
+        <is>
+          <t>cicilan</t>
+        </is>
+      </c>
+      <c r="F17" s="46" t="n">
+        <v>83333</v>
+      </c>
+      <c r="G17" s="46" t="n">
+        <v>29167</v>
+      </c>
+      <c r="H17" s="46" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I17" s="44" t="n">
+        <v>562500</v>
+      </c>
+      <c r="J17" s="42" t="inlineStr">
+        <is>
+          <t>dibayar</t>
+        </is>
+      </c>
+      <c r="K17" s="41" t="inlineStr">
+        <is>
+          <t>angsuran mingguan ke-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1" s="32">
+      <c r="A18" s="41" t="inlineStr">
+        <is>
+          <t>BYR-20260915-006</t>
+        </is>
+      </c>
+      <c r="B18" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0006</t>
+        </is>
+      </c>
+      <c r="C18" s="43" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="D18" s="41" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" s="42" t="inlineStr">
+        <is>
+          <t>cicilan</t>
+        </is>
+      </c>
+      <c r="F18" s="46" t="n">
+        <v>83333</v>
+      </c>
+      <c r="G18" s="46" t="n">
+        <v>29167</v>
+      </c>
+      <c r="H18" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="44" t="n">
+        <v>450000</v>
+      </c>
+      <c r="J18" s="42" t="inlineStr">
+        <is>
+          <t>dibayar</t>
+        </is>
+      </c>
+      <c r="K18" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">angsuran mingguan ke-4 </t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="32">
+      <c r="A19" s="41" t="inlineStr">
+        <is>
+          <t>BYR-PELUNASAN-001</t>
+        </is>
+      </c>
+      <c r="B19" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261018-0016</t>
+        </is>
+      </c>
+      <c r="C19" s="43" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="D19" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="42" t="inlineStr">
+        <is>
+          <t>pelunasan</t>
+        </is>
+      </c>
+      <c r="F19" s="46" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="G19" s="46" t="n">
+        <v>470000</v>
+      </c>
+      <c r="H19" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="44" t="n">
+        <v>3470000</v>
+      </c>
+      <c r="J19" s="42" t="inlineStr">
+        <is>
+          <t>dibayar</t>
+        </is>
+      </c>
+      <c r="K19" s="41" t="inlineStr">
+        <is>
+          <t>Pelunasan</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="41" t="inlineStr">
+        <is>
+          <t>BYR-20260915-014</t>
+        </is>
+      </c>
+      <c r="B20" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0014</t>
+        </is>
+      </c>
+      <c r="C20" s="43" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+      <c r="D20" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" s="42" t="inlineStr">
+        <is>
+          <t>cicilan</t>
+        </is>
+      </c>
+      <c r="F20" s="46" t="n">
+        <v>83333</v>
+      </c>
+      <c r="G20" s="46" t="n">
+        <v>29167</v>
+      </c>
+      <c r="H20" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="44" t="n">
+        <v>675000</v>
+      </c>
+      <c r="J20" s="42" t="inlineStr">
+        <is>
+          <t>dibayar</t>
+        </is>
+      </c>
+      <c r="K20" s="41" t="inlineStr">
+        <is>
+          <t>angsuran mingguan ke-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="41" t="inlineStr">
+        <is>
+          <t>BYR-20261027-NOV</t>
+        </is>
+      </c>
+      <c r="B21" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0005</t>
+        </is>
+      </c>
+      <c r="C21" s="43" t="inlineStr">
+        <is>
+          <t>27/10/2026</t>
+        </is>
+      </c>
+      <c r="D21" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" s="42" t="inlineStr">
+        <is>
+          <t>cicilan</t>
+        </is>
+      </c>
+      <c r="F21" s="46" t="n">
+        <v>83333</v>
+      </c>
+      <c r="G21" s="46" t="n">
+        <v>29167</v>
+      </c>
+      <c r="H21" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="44" t="n">
+        <v>112500</v>
+      </c>
+      <c r="J21" s="42" t="inlineStr">
+        <is>
+          <t>dibayar</t>
+        </is>
+      </c>
+      <c r="K21" s="41" t="inlineStr">
+        <is>
+          <t>Pembayaran Novitasari; angsuran ke-6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="41" t="inlineStr">
+        <is>
+          <t>BYR-20261027-SUM</t>
+        </is>
+      </c>
+      <c r="B22" s="42" t="inlineStr">
         <is>
           <t>PJN-20261013-0002</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
-        <is>
-          <t>12/10/2026</t>
-        </is>
-      </c>
-      <c r="D4" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="39" t="inlineStr">
+      <c r="C22" s="43" t="inlineStr">
+        <is>
+          <t>27/10/2026</t>
+        </is>
+      </c>
+      <c r="D22" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="42" t="inlineStr">
         <is>
           <t>cicilan</t>
         </is>
       </c>
-      <c r="F4" s="39" t="n">
+      <c r="F22" s="46" t="n">
         <v>166667</v>
       </c>
-      <c r="G4" s="39" t="n">
+      <c r="G22" s="46" t="n">
         <v>58333</v>
       </c>
-      <c r="H4" s="39" t="n">
+      <c r="H22" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="39" t="n">
+      <c r="I22" s="44" t="n">
         <v>225000</v>
       </c>
-      <c r="J4" s="39" t="inlineStr">
+      <c r="J22" s="42" t="inlineStr">
         <is>
           <t>dibayar</t>
         </is>
       </c>
-      <c r="K4" s="39" t="inlineStr">
-        <is>
-          <t>angsuran mingguan ke-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1" s="32">
-      <c r="A5" s="39" t="inlineStr">
-        <is>
-          <t>BYR-20260915-003</t>
-        </is>
-      </c>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="K22" s="41" t="inlineStr">
+        <is>
+          <t>Pembayaran Sumiati; angsuran ke-2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="41" t="inlineStr">
+        <is>
+          <t>BYR-20261028-DESINTA-6</t>
+        </is>
+      </c>
+      <c r="B23" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0009</t>
+        </is>
+      </c>
+      <c r="C23" s="43" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="D23" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" s="42" t="inlineStr">
+        <is>
+          <t>cicilan</t>
+        </is>
+      </c>
+      <c r="F23" s="46" t="n">
+        <v>166667</v>
+      </c>
+      <c r="G23" s="46" t="n">
+        <v>58333</v>
+      </c>
+      <c r="H23" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="44" t="n">
+        <v>225000</v>
+      </c>
+      <c r="J23" s="42" t="inlineStr">
+        <is>
+          <t>dibayar</t>
+        </is>
+      </c>
+      <c r="K23" s="41" t="inlineStr">
+        <is>
+          <t>Pemasukan 28/10 Desinta 225.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="41" t="inlineStr">
+        <is>
+          <t>BYR-20261028-PUJI-6</t>
+        </is>
+      </c>
+      <c r="B24" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0004</t>
+        </is>
+      </c>
+      <c r="C24" s="43" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="D24" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="E24" s="42" t="inlineStr">
+        <is>
+          <t>cicilan</t>
+        </is>
+      </c>
+      <c r="F24" s="46" t="n">
+        <v>83333</v>
+      </c>
+      <c r="G24" s="46" t="n">
+        <v>29167</v>
+      </c>
+      <c r="H24" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="44" t="n">
+        <v>112500</v>
+      </c>
+      <c r="J24" s="42" t="inlineStr">
+        <is>
+          <t>dibayar</t>
+        </is>
+      </c>
+      <c r="K24" s="41" t="inlineStr">
+        <is>
+          <t>Pemasukan 28/10 Puji Wahyuni 112.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="41" t="inlineStr">
+        <is>
+          <t>BYR-20261029-ELIS-7</t>
+        </is>
+      </c>
+      <c r="B25" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0013</t>
+        </is>
+      </c>
+      <c r="C25" s="43" t="n">
+        <v>46324</v>
+      </c>
+      <c r="D25" s="41" t="n">
+        <v>7</v>
+      </c>
+      <c r="E25" s="42" t="inlineStr">
+        <is>
+          <t>cicilan</t>
+        </is>
+      </c>
+      <c r="F25" s="46" t="n">
+        <v>83333</v>
+      </c>
+      <c r="G25" s="46" t="n">
+        <v>29167</v>
+      </c>
+      <c r="H25" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="44" t="n">
+        <v>112500</v>
+      </c>
+      <c r="J25" s="42" t="inlineStr">
+        <is>
+          <t>dibayar</t>
+        </is>
+      </c>
+      <c r="K25" s="41" t="inlineStr">
+        <is>
+          <t>Angsuran mingguan 29/10 Elis Lutfiana (Lunas normal).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="41" t="inlineStr">
+        <is>
+          <t>BYR-20261029-NOVIANI-6</t>
+        </is>
+      </c>
+      <c r="B26" s="42" t="inlineStr">
         <is>
           <t>PJN-20261013-0003</t>
         </is>
       </c>
-      <c r="C5" s="39" t="inlineStr">
-        <is>
-          <t>21/10/2026</t>
-        </is>
-      </c>
-      <c r="D5" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" s="39" t="inlineStr">
+      <c r="C26" s="43" t="n">
+        <v>46324</v>
+      </c>
+      <c r="D26" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" s="42" t="inlineStr">
         <is>
           <t>cicilan</t>
         </is>
       </c>
-      <c r="F5" s="39" t="n">
+      <c r="F26" s="46" t="n">
         <v>166667</v>
       </c>
-      <c r="G5" s="39" t="n">
+      <c r="G26" s="46" t="n">
         <v>58333</v>
       </c>
-      <c r="H5" s="39" t="n">
+      <c r="H26" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="39" t="n">
-        <v>1125000</v>
-      </c>
-      <c r="J5" s="39" t="inlineStr">
+      <c r="I26" s="44" t="n">
+        <v>225000</v>
+      </c>
+      <c r="J26" s="42" t="inlineStr">
         <is>
           <t>dibayar</t>
         </is>
       </c>
-      <c r="K5" s="39" t="inlineStr">
-        <is>
-          <t>angsuran mingguan ke-5</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="32">
-      <c r="A6" s="39" t="inlineStr">
-        <is>
-          <t>BYR-20260915-004</t>
-        </is>
-      </c>
-      <c r="B6" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0004</t>
-        </is>
-      </c>
-      <c r="C6" s="39" t="inlineStr">
-        <is>
-          <t>22/10/2026</t>
-        </is>
-      </c>
-      <c r="D6" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="39" t="inlineStr">
-        <is>
-          <t>cicilan</t>
-        </is>
-      </c>
-      <c r="F6" s="39" t="n">
-        <v>83333</v>
-      </c>
-      <c r="G6" s="39" t="n">
-        <v>29167</v>
-      </c>
-      <c r="H6" s="39" t="n">
-        <v>1500</v>
-      </c>
-      <c r="I6" s="39" t="n">
-        <v>562500</v>
-      </c>
-      <c r="J6" s="39" t="inlineStr">
+      <c r="K26" s="41" t="inlineStr">
+        <is>
+          <t>Angsuran mingguan 29/10 Noviani 225.000 (Lunas normal).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="41" t="inlineStr">
+        <is>
+          <t>BYR-20261029-UMAINAH-PEL</t>
+        </is>
+      </c>
+      <c r="B27" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0001</t>
+        </is>
+      </c>
+      <c r="C27" s="43" t="n">
+        <v>46324</v>
+      </c>
+      <c r="D27" s="41" t="n">
+        <v>7</v>
+      </c>
+      <c r="E27" s="42" t="inlineStr">
+        <is>
+          <t>pelunasan</t>
+        </is>
+      </c>
+      <c r="F27" s="46" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="G27" s="46" t="n">
+        <v>368000</v>
+      </c>
+      <c r="H27" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="44" t="n">
+        <v>1368000</v>
+      </c>
+      <c r="J27" s="42" t="inlineStr">
         <is>
           <t>dibayar</t>
         </is>
       </c>
-      <c r="K6" s="39" t="inlineStr">
-        <is>
-          <t>angsuran mingguan ke-5</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1" s="32" thickBot="1">
-      <c r="A7" s="39" t="inlineStr">
-        <is>
-          <t>BYR-20260915-005</t>
-        </is>
-      </c>
-      <c r="B7" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0005</t>
-        </is>
-      </c>
-      <c r="C7" s="39" t="inlineStr">
-        <is>
-          <t>23/10/2026</t>
-        </is>
-      </c>
-      <c r="D7" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="E7" s="39" t="inlineStr">
-        <is>
-          <t>cicilan</t>
-        </is>
-      </c>
-      <c r="F7" s="39" t="n">
-        <v>83333</v>
-      </c>
-      <c r="G7" s="39" t="n">
-        <v>29167</v>
-      </c>
-      <c r="H7" s="39" t="n">
-        <v>1500</v>
-      </c>
-      <c r="I7" s="39" t="n">
-        <v>562500</v>
-      </c>
-      <c r="J7" s="39" t="inlineStr">
-        <is>
-          <t>dibayar</t>
-        </is>
-      </c>
-      <c r="K7" s="39" t="inlineStr">
-        <is>
-          <t>angsuran mingguan ke-5</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="32">
-      <c r="A8" s="39" t="inlineStr">
-        <is>
-          <t>BYR-20260915-006</t>
-        </is>
-      </c>
-      <c r="B8" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0006</t>
-        </is>
-      </c>
-      <c r="C8" s="39" t="inlineStr">
-        <is>
-          <t>23/10/2026</t>
-        </is>
-      </c>
-      <c r="D8" s="39" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" s="39" t="inlineStr">
-        <is>
-          <t>cicilan</t>
-        </is>
-      </c>
-      <c r="F8" s="39" t="n">
-        <v>83333</v>
-      </c>
-      <c r="G8" s="39" t="n">
-        <v>29167</v>
-      </c>
-      <c r="H8" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="39" t="n">
-        <v>450000</v>
-      </c>
-      <c r="J8" s="39" t="inlineStr">
-        <is>
-          <t>dibayar</t>
-        </is>
-      </c>
-      <c r="K8" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">angsuran mingguan ke-4 </t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="32">
-      <c r="A9" s="39" t="inlineStr">
-        <is>
-          <t>BYR-20260915-007</t>
-        </is>
-      </c>
-      <c r="B9" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0007</t>
-        </is>
-      </c>
-      <c r="C9" s="39" t="inlineStr">
-        <is>
-          <t>19/10/2026</t>
-        </is>
-      </c>
-      <c r="D9" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="39" t="inlineStr">
-        <is>
-          <t>cicilan</t>
-        </is>
-      </c>
-      <c r="F9" s="39" t="n">
-        <v>83333</v>
-      </c>
-      <c r="G9" s="39" t="n">
-        <v>29167</v>
-      </c>
-      <c r="H9" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="39" t="n">
-        <v>337500</v>
-      </c>
-      <c r="J9" s="39" t="inlineStr">
-        <is>
-          <t>dibayar</t>
-        </is>
-      </c>
-      <c r="K9" s="39" t="inlineStr">
-        <is>
-          <t>angsuran mingguan ke-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="32">
-      <c r="A10" s="39" t="inlineStr">
-        <is>
-          <t>BYR-20260915-008</t>
-        </is>
-      </c>
-      <c r="B10" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0008</t>
-        </is>
-      </c>
-      <c r="C10" s="39" t="inlineStr">
-        <is>
-          <t>21/10/2026</t>
-        </is>
-      </c>
-      <c r="D10" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" s="39" t="inlineStr">
-        <is>
-          <t>cicilan</t>
-        </is>
-      </c>
-      <c r="F10" s="39" t="n">
-        <v>83333</v>
-      </c>
-      <c r="G10" s="39" t="n">
-        <v>29167</v>
-      </c>
-      <c r="H10" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="39" t="n">
-        <v>337500</v>
-      </c>
-      <c r="J10" s="39" t="inlineStr">
-        <is>
-          <t>dibayar</t>
-        </is>
-      </c>
-      <c r="K10" s="39" t="inlineStr">
-        <is>
-          <t>angsuran mingguan ke-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1" s="32">
-      <c r="A11" s="39" t="inlineStr">
-        <is>
-          <t>BYR-20260915-009</t>
-        </is>
-      </c>
-      <c r="B11" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0009</t>
-        </is>
-      </c>
-      <c r="C11" s="39" t="inlineStr">
-        <is>
-          <t>22/10/2026</t>
-        </is>
-      </c>
-      <c r="D11" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" s="39" t="inlineStr">
-        <is>
-          <t>cicilan</t>
-        </is>
-      </c>
-      <c r="F11" s="39" t="n">
-        <v>166667</v>
-      </c>
-      <c r="G11" s="39" t="n">
-        <v>58333</v>
-      </c>
-      <c r="H11" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="39" t="n">
-        <v>450000</v>
-      </c>
-      <c r="J11" s="39" t="inlineStr">
-        <is>
-          <t>dibayar</t>
-        </is>
-      </c>
-      <c r="K11" s="39" t="inlineStr">
-        <is>
-          <t>angsuran mingguan ke-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1" s="32">
-      <c r="A12" s="39" t="inlineStr">
-        <is>
-          <t>BYR-20260915-010</t>
-        </is>
-      </c>
-      <c r="B12" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0010</t>
-        </is>
-      </c>
-      <c r="C12" s="39" t="inlineStr">
-        <is>
-          <t>12/10/2026</t>
-        </is>
-      </c>
-      <c r="D12" s="39" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" s="39" t="inlineStr">
-        <is>
-          <t>cicilan</t>
-        </is>
-      </c>
-      <c r="F12" s="39" t="n">
-        <v>125000</v>
-      </c>
-      <c r="G12" s="39" t="n">
-        <v>31250</v>
-      </c>
-      <c r="H12" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="39" t="n">
-        <v>625000</v>
-      </c>
-      <c r="J12" s="39" t="inlineStr">
-        <is>
-          <t>dibayar</t>
-        </is>
-      </c>
-      <c r="K12" s="39" t="inlineStr">
-        <is>
-          <t>angsuran mingguan ke-4 ke 5nya pelunasan</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="32">
-      <c r="A13" s="39" t="inlineStr">
-        <is>
-          <t>BYR-20260915-011</t>
-        </is>
-      </c>
-      <c r="B13" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0011</t>
-        </is>
-      </c>
-      <c r="C13" s="39" t="inlineStr">
-        <is>
-          <t>22/10/2026</t>
-        </is>
-      </c>
-      <c r="D13" s="39" t="n">
-        <v>6</v>
-      </c>
-      <c r="E13" s="39" t="inlineStr">
-        <is>
-          <t>cicilan</t>
-        </is>
-      </c>
-      <c r="F13" s="39" t="n">
-        <v>83333</v>
-      </c>
-      <c r="G13" s="39" t="n">
-        <v>29167</v>
-      </c>
-      <c r="H13" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="39" t="n">
-        <v>675000</v>
-      </c>
-      <c r="J13" s="39" t="inlineStr">
-        <is>
-          <t>dibayar</t>
-        </is>
-      </c>
-      <c r="K13" s="39" t="inlineStr">
-        <is>
-          <t>angsuran mingguan ke-6</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="32">
-      <c r="A14" s="39" t="inlineStr">
-        <is>
-          <t>BYR-20260915-012</t>
-        </is>
-      </c>
-      <c r="B14" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0012</t>
-        </is>
-      </c>
-      <c r="C14" s="39" t="inlineStr">
-        <is>
-          <t>22/10/2026</t>
-        </is>
-      </c>
-      <c r="D14" s="39" t="n">
-        <v>6</v>
-      </c>
-      <c r="E14" s="39" t="inlineStr">
-        <is>
-          <t>cicilan</t>
-        </is>
-      </c>
-      <c r="F14" s="39" t="n">
-        <v>83333</v>
-      </c>
-      <c r="G14" s="39" t="n">
-        <v>29167</v>
-      </c>
-      <c r="H14" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="39" t="n">
-        <v>675000</v>
-      </c>
-      <c r="J14" s="39" t="inlineStr">
-        <is>
-          <t>dibayar</t>
-        </is>
-      </c>
-      <c r="K14" s="39" t="inlineStr">
-        <is>
-          <t>angsuran mingguan ke-6</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="32">
-      <c r="A15" s="39" t="inlineStr">
-        <is>
-          <t>BYR-20260915-013</t>
-        </is>
-      </c>
-      <c r="B15" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0013</t>
-        </is>
-      </c>
-      <c r="C15" s="39" t="inlineStr">
-        <is>
-          <t>22/10/2026</t>
-        </is>
-      </c>
-      <c r="D15" s="39" t="n">
-        <v>6</v>
-      </c>
-      <c r="E15" s="39" t="inlineStr">
-        <is>
-          <t>cicilan</t>
-        </is>
-      </c>
-      <c r="F15" s="39" t="n">
-        <v>83333</v>
-      </c>
-      <c r="G15" s="39" t="n">
-        <v>29167</v>
-      </c>
-      <c r="H15" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="39" t="n">
-        <v>675000</v>
-      </c>
-      <c r="J15" s="39" t="inlineStr">
-        <is>
-          <t>dibayar</t>
-        </is>
-      </c>
-      <c r="K15" s="39" t="inlineStr">
-        <is>
-          <t>angsuran mingguan ke-6</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1" s="32" thickBot="1">
-      <c r="A16" s="39" t="inlineStr">
-        <is>
-          <t>BYR-20260915-014</t>
-        </is>
-      </c>
-      <c r="B16" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0014</t>
-        </is>
-      </c>
-      <c r="C16" s="39" t="inlineStr">
-        <is>
-          <t>24/10/2026</t>
-        </is>
-      </c>
-      <c r="D16" s="39" t="n">
-        <v>6</v>
-      </c>
-      <c r="E16" s="39" t="inlineStr">
-        <is>
-          <t>cicilan</t>
-        </is>
-      </c>
-      <c r="F16" s="39" t="n">
-        <v>83333</v>
-      </c>
-      <c r="G16" s="39" t="n">
-        <v>29167</v>
-      </c>
-      <c r="H16" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="39" t="n">
-        <v>675000</v>
-      </c>
-      <c r="J16" s="39" t="inlineStr">
-        <is>
-          <t>dibayar</t>
-        </is>
-      </c>
-      <c r="K16" s="39" t="inlineStr">
-        <is>
-          <t>angsuran mingguan ke-6</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="39" t="inlineStr">
-        <is>
-          <t>BYR-PELUNASAN-001</t>
-        </is>
-      </c>
-      <c r="B17" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261018-0016</t>
-        </is>
-      </c>
-      <c r="C17" s="39" t="inlineStr">
-        <is>
-          <t>23/10/2026</t>
-        </is>
-      </c>
-      <c r="D17" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="39" t="inlineStr">
-        <is>
-          <t>pelunasan</t>
-        </is>
-      </c>
-      <c r="F17" s="39" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="G17" s="39" t="n">
-        <v>470000</v>
-      </c>
-      <c r="H17" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="39" t="n">
-        <v>3470000</v>
-      </c>
-      <c r="J17" s="39" t="inlineStr">
-        <is>
-          <t>dibayar</t>
-        </is>
-      </c>
-      <c r="K17" s="39" t="inlineStr">
-        <is>
-          <t>Pelunasan</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1" s="32">
-      <c r="A18" s="39" t="inlineStr">
-        <is>
-          <t>BYR-20260915-015</t>
-        </is>
-      </c>
-      <c r="B18" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0010</t>
-        </is>
-      </c>
-      <c r="C18" s="39" t="inlineStr">
-        <is>
-          <t>19/10/2026</t>
-        </is>
-      </c>
-      <c r="D18" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="E18" s="39" t="inlineStr">
-        <is>
-          <t>pelunasan</t>
-        </is>
-      </c>
-      <c r="F18" s="39" t="n">
-        <v>125000</v>
-      </c>
-      <c r="G18" s="39" t="n">
-        <v>31250</v>
-      </c>
-      <c r="H18" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="39" t="n">
-        <v>625000</v>
-      </c>
-      <c r="J18" s="39" t="inlineStr">
-        <is>
-          <t>dibayar</t>
-        </is>
-      </c>
-      <c r="K18" s="39" t="inlineStr">
-        <is>
-          <t>Pelunasan; ID diperbaiki karena duplikat.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="32">
-      <c r="A19" s="39" t="inlineStr">
-        <is>
-          <t>BYR-20261027-NOV</t>
-        </is>
-      </c>
-      <c r="B19" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0005</t>
-        </is>
-      </c>
-      <c r="C19" s="39" t="inlineStr">
-        <is>
-          <t>27/10/2026</t>
-        </is>
-      </c>
-      <c r="D19" s="39" t="n">
-        <v>6</v>
-      </c>
-      <c r="E19" s="39" t="inlineStr">
-        <is>
-          <t>cicilan</t>
-        </is>
-      </c>
-      <c r="F19" s="39" t="n">
-        <v>83333</v>
-      </c>
-      <c r="G19" s="39" t="n">
-        <v>29167</v>
-      </c>
-      <c r="H19" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="39" t="n">
-        <v>112500</v>
-      </c>
-      <c r="J19" s="39" t="inlineStr">
-        <is>
-          <t>dibayar</t>
-        </is>
-      </c>
-      <c r="K19" s="39" t="inlineStr">
-        <is>
-          <t>Pembayaran Novitasari; angsuran ke-6.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="39" t="inlineStr">
-        <is>
-          <t>BYR-20261027-SUM</t>
-        </is>
-      </c>
-      <c r="B20" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0002</t>
-        </is>
-      </c>
-      <c r="C20" s="39" t="inlineStr">
-        <is>
-          <t>27/10/2026</t>
-        </is>
-      </c>
-      <c r="D20" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" s="39" t="inlineStr">
-        <is>
-          <t>cicilan</t>
-        </is>
-      </c>
-      <c r="F20" s="39" t="n">
-        <v>166667</v>
-      </c>
-      <c r="G20" s="39" t="n">
-        <v>58333</v>
-      </c>
-      <c r="H20" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="39" t="n">
-        <v>225000</v>
-      </c>
-      <c r="J20" s="39" t="inlineStr">
-        <is>
-          <t>dibayar</t>
-        </is>
-      </c>
-      <c r="K20" s="39" t="inlineStr">
-        <is>
-          <t>Pembayaran Sumiati; angsuran ke-2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="39" t="inlineStr">
-        <is>
-          <t>BYR-20261028-DESINTA-6</t>
-        </is>
-      </c>
-      <c r="B21" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0009</t>
-        </is>
-      </c>
-      <c r="C21" s="39" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="D21" s="39" t="n">
-        <v>6</v>
-      </c>
-      <c r="E21" s="39" t="inlineStr">
-        <is>
-          <t>cicilan</t>
-        </is>
-      </c>
-      <c r="F21" s="39" t="n">
-        <v>166667</v>
-      </c>
-      <c r="G21" s="39" t="n">
-        <v>58333</v>
-      </c>
-      <c r="H21" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="39" t="n">
-        <v>225000</v>
-      </c>
-      <c r="J21" s="39" t="inlineStr">
-        <is>
-          <t>dibayar</t>
-        </is>
-      </c>
-      <c r="K21" s="39" t="inlineStr">
-        <is>
-          <t>Pemasukan 28/10 Desinta 225.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="39" t="inlineStr">
-        <is>
-          <t>BYR-20261028-PUJI-6</t>
-        </is>
-      </c>
-      <c r="B22" s="39" t="inlineStr">
-        <is>
-          <t>PJN-20261013-0004</t>
-        </is>
-      </c>
-      <c r="C22" s="39" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="D22" s="39" t="n">
-        <v>6</v>
-      </c>
-      <c r="E22" s="39" t="inlineStr">
-        <is>
-          <t>cicilan</t>
-        </is>
-      </c>
-      <c r="F22" s="39" t="n">
-        <v>83333</v>
-      </c>
-      <c r="G22" s="39" t="n">
-        <v>29167</v>
-      </c>
-      <c r="H22" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="39" t="n">
-        <v>112500</v>
-      </c>
-      <c r="J22" s="39" t="inlineStr">
-        <is>
-          <t>dibayar</t>
-        </is>
-      </c>
-      <c r="K22" s="39" t="inlineStr">
-        <is>
-          <t>Pemasukan 28/10 Puji Wahyuni 112.500</t>
+      <c r="K27" s="41" t="inlineStr">
+        <is>
+          <t>Pelunasan sisa tenor UMAINAH 29/10 (status cicilan sebelumnya = Lunas normal; sisa = Pelunasan).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:K1000"/>
+  <autoFilter ref="A2:K27"/>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
   </mergeCells>

--- a/Template_Migrasi_Final_Revisi.xlsx
+++ b/Template_Migrasi_Final_Revisi.xlsx
@@ -43,7 +43,7 @@
     <numFmt numFmtId="164" formatCode="\R\p\ #,##0;[Red]\-\R\p\ #,##0"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="Rp #,##0;[Red]-Rp #,##0"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -1692,7 +1692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" style="32" min="1" max="1"/>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SOLIKAH denda 1500 tgl 25/09/2026; MASLUKAH denda 1500 tgl 15/10/2026 (Angsuran_Historis → laporan denda).</t>
+          <t>Laporan denda historis HANYA 2 nama: SOLIKAH 1.500 (25/09/2026) + MASLUKAH 1.500 (15/10/2026). Denda berjalan di-cut-off = 0 (manual).</t>
         </is>
       </c>
     </row>
@@ -1864,6 +1864,30 @@
       <c r="B14" t="inlineStr">
         <is>
           <t>Jangan hapus uploads/ saat reset. Path di Excel opsional jika cadangan kode anggota sama.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SOLIKAH_MASLUKAH_CICILAN</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Solikah &amp; Maslukah cicilan 4-6 sudah dibayar di lapangan → ditambah BYR-20261030-SOLIKAH-6 &amp; BYR-20261029-MASLUKAH-6 (total 337.500 tiap orang).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DENDA_CUTOFF</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Setelah import, sisa cicilan belum lunas dibekukan denda=0 + denda_manual=1 agar tidak muncul tagihan otomatis sebelum go-live.</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col width="18" customWidth="1" style="32" min="1" max="1"/>
@@ -4281,7 +4305,7 @@
       </c>
       <c r="K3" s="41" t="inlineStr">
         <is>
-          <t>DENDA 1.500 Solikah tgl 25/09/2026 — wajib muncul di Laporan Denda.</t>
+          <t>DENDA telat 1 hari Rp 1.500 — SOLIKAH (25/09/2026). Siap tampil di Laporan Denda.</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4444,7 @@
       </c>
       <c r="K6" s="41" t="inlineStr">
         <is>
-          <t>DENDA 1.500 Maslukah tgl 15/10/2026 — wajib muncul di Laporan Denda.</t>
+          <t>DENDA telat 1 hari Rp 1.500 — MASLUKAH (15/10/2026). Siap tampil di Laporan Denda.</t>
         </is>
       </c>
     </row>
@@ -4690,7 +4714,7 @@
         <v>29167</v>
       </c>
       <c r="H12" s="46" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="I12" s="44" t="n">
         <v>562500</v>
@@ -4925,7 +4949,7 @@
         <v>29167</v>
       </c>
       <c r="H17" s="46" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="I17" s="44" t="n">
         <v>562500</v>
@@ -5402,6 +5426,96 @@
       <c r="K27" s="41" t="inlineStr">
         <is>
           <t>Pelunasan sisa tenor UMAINAH 29/10 (status cicilan sebelumnya = Lunas normal; sisa = Pelunasan).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="41" t="inlineStr">
+        <is>
+          <t>BYR-20261030-SOLIKAH-6</t>
+        </is>
+      </c>
+      <c r="B28" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0007</t>
+        </is>
+      </c>
+      <c r="C28" s="43" t="n">
+        <v>46325</v>
+      </c>
+      <c r="D28" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" s="42" t="inlineStr">
+        <is>
+          <t>cicilan</t>
+        </is>
+      </c>
+      <c r="F28" s="46" t="n">
+        <v>83333</v>
+      </c>
+      <c r="G28" s="46" t="n">
+        <v>29167</v>
+      </c>
+      <c r="H28" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="44" t="n">
+        <v>337500</v>
+      </c>
+      <c r="J28" s="42" t="inlineStr">
+        <is>
+          <t>dibayar</t>
+        </is>
+      </c>
+      <c r="K28" s="41" t="inlineStr">
+        <is>
+          <t>cicilan 4-6 Solikah sudah dibayar (konfirmasi user)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="41" t="inlineStr">
+        <is>
+          <t>BYR-20261029-MASLUKAH-6</t>
+        </is>
+      </c>
+      <c r="B29" s="42" t="inlineStr">
+        <is>
+          <t>PJN-20261013-0008</t>
+        </is>
+      </c>
+      <c r="C29" s="43" t="n">
+        <v>46324</v>
+      </c>
+      <c r="D29" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="E29" s="42" t="inlineStr">
+        <is>
+          <t>cicilan</t>
+        </is>
+      </c>
+      <c r="F29" s="46" t="n">
+        <v>83333</v>
+      </c>
+      <c r="G29" s="46" t="n">
+        <v>29167</v>
+      </c>
+      <c r="H29" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="44" t="n">
+        <v>337500</v>
+      </c>
+      <c r="J29" s="42" t="inlineStr">
+        <is>
+          <t>dibayar</t>
+        </is>
+      </c>
+      <c r="K29" s="41" t="inlineStr">
+        <is>
+          <t>cicilan 4-6 Maslukah sudah dibayar (konfirmasi user)</t>
         </is>
       </c>
     </row>

--- a/Template_Migrasi_Final_Revisi.xlsx
+++ b/Template_Migrasi_Final_Revisi.xlsx
@@ -39,11 +39,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="\R\p\ #,##0;[Red]\-\R\p\ #,##0"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="Rp #,##0;[Red]-Rp #,##0"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -1870,12 +1869,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SOLIKAH_MASLUKAH_CICILAN</t>
+          <t>SOLIKAH_CICILAN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Solikah &amp; Maslukah cicilan 4-6 sudah dibayar di lapangan → ditambah BYR-20261030-SOLIKAH-6 &amp; BYR-20261029-MASLUKAH-6 (total 337.500 tiap orang).</t>
+          <t>SOLIKAH: lunas sampai cicilan 5 saja (BYR-20261023-SOLIKAH-5). Cicilan 6 jatuh tempo 30/10/2026 BELUM lunas agar muncul di angsuran Jumat. Setelah bayar hari ini sisa 6 cicilan (ke 7-12). Hapus BYR-20261030-SOLIKAH-6 yang keliru.</t>
         </is>
       </c>
     </row>
@@ -5432,16 +5431,16 @@
     <row r="28">
       <c r="A28" s="41" t="inlineStr">
         <is>
-          <t>BYR-20261030-SOLIKAH-6</t>
+          <t>BYR-20261029-MASLUKAH-6</t>
         </is>
       </c>
       <c r="B28" s="42" t="inlineStr">
         <is>
-          <t>PJN-20261013-0007</t>
+          <t>PJN-20261013-0008</t>
         </is>
       </c>
       <c r="C28" s="43" t="n">
-        <v>46325</v>
+        <v>46324</v>
       </c>
       <c r="D28" s="41" t="n">
         <v>6</v>
@@ -5470,26 +5469,26 @@
       </c>
       <c r="K28" s="41" t="inlineStr">
         <is>
-          <t>cicilan 4-6 Solikah sudah dibayar (konfirmasi user)</t>
+          <t>cicilan 4-6 Maslukah sudah dibayar (konfirmasi user)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="41" t="inlineStr">
         <is>
-          <t>BYR-20261029-MASLUKAH-6</t>
+          <t>BYR-20261023-SOLIKAH-5</t>
         </is>
       </c>
       <c r="B29" s="42" t="inlineStr">
         <is>
-          <t>PJN-20261013-0008</t>
+          <t>PJN-20261013-0007</t>
         </is>
       </c>
       <c r="C29" s="43" t="n">
-        <v>46324</v>
+        <v>46318</v>
       </c>
       <c r="D29" s="41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E29" s="42" t="inlineStr">
         <is>
@@ -5506,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="44" t="n">
-        <v>337500</v>
+        <v>225000</v>
       </c>
       <c r="J29" s="42" t="inlineStr">
         <is>
@@ -5515,7 +5514,7 @@
       </c>
       <c r="K29" s="41" t="inlineStr">
         <is>
-          <t>cicilan 4-6 Maslukah sudah dibayar (konfirmasi user)</t>
+          <t>cicilan 4-5 Solikah sudah dibayar; ke-6 (30/10) belum — muncul di angsuran hari ini</t>
         </is>
       </c>
     </row>
